--- a/Korp/Matriz/2026-09/Conciliacao_Sicredi_Matriz_09-2026_conta_sugerida.xlsx
+++ b/Korp/Matriz/2026-09/Conciliacao_Sicredi_Matriz_09-2026_conta_sugerida.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Faltam no razão" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conta sugerida'!$A$1:$P$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conta sugerida'!$A$1:$Q$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Faltam no razão'!$A$1:$L$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -56,12 +56,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -664,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P150"/>
+  <dimension ref="A1:Q150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -678,11 +678,12 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="42" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="70" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -743,25 +744,30 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Área do CC</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>Cód. reduzido sugerido</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Nome da conta sugerida</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Confiança</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
@@ -815,27 +821,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="n">
         <v>3050</v>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>2.1.1.1.5.10</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>Vale Transporte Funcionários</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P2" s="4" t="inlineStr">
-        <is>
-          <t>Vale-transporte de funcionários.</t>
+      <c r="P2" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
+          <t>Vale-transporte de funcionários. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -887,25 +898,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="n">
         <v>2688</v>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.49</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>Energia Eletrica</t>
         </is>
       </c>
-      <c r="O3" s="7" t="inlineStr">
+      <c r="P3" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>Energia elétrica.</t>
         </is>
@@ -959,27 +975,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="n">
         <v>3046</v>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>2.1.1.1.5.6</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Refeições</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t>Vale-refeição/alimentação (Benefícios - Refeições). Alternativa: 3043 PAT.</t>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>Vale-refeição/alimentação (Benefícios - Refeições). Alternativa: 3043 PAT. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -1031,27 +1052,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="n">
         <v>2698</v>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>3.1.3.3.1.1</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>Despesas Bancarias</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>Tarifa bancária.</t>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>Tarifa bancária. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -1095,25 +1121,30 @@
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>sem CC</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="n">
         <v>2637</v>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.2.1.10</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>Serviços Prestados por Terceiros (Adm)</t>
         </is>
       </c>
-      <c r="O6" s="9" t="inlineStr">
+      <c r="P6" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>Locação de equipamentos de informática: confirmar (2637 serviços de terceiros ou conta de locação).</t>
         </is>
@@ -1167,27 +1198,32 @@
           <t>CC833</t>
         </is>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="n">
         <v>2587</v>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>3.1.3.1.2.1.4</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>Despesas com Viagens/Hospedagem</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr">
-        <is>
-          <t>Hospedagem (despesa comercial). Se for administrativa: 2647 Viagens.</t>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>Hospedagem (despesa comercial). Se for administrativa: 2647 Viagens. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -1239,27 +1275,32 @@
           <t>CC645</t>
         </is>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="n">
         <v>2587</v>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>3.1.3.1.2.1.4</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>Despesas com Viagens/Hospedagem</t>
         </is>
       </c>
-      <c r="O8" s="8" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
-        <is>
-          <t>Hospedagem (despesa comercial). Se for administrativa: 2647 Viagens.</t>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>Hospedagem (despesa comercial). Se for administrativa: 2647 Viagens. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -1311,27 +1352,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="n">
         <v>2436</v>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>1.1.2.1.1</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>Clientes a Receber</t>
         </is>
       </c>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr">
-        <is>
-          <t>Baixa de duplicata/mensalidade de cliente.</t>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>Recebimento de cliente (baixa de duplicata/mensalidade). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -1375,25 +1421,30 @@
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="n">
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>sem CC</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="n">
         <v>2649</v>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.10</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>Bens de Pequeno Valor</t>
         </is>
       </c>
-      <c r="O10" s="9" t="inlineStr">
+      <c r="P10" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr">
+      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>Compra AC (sem categoria gerencial no extrato): bem de pequeno valor/material. Confirmar.</t>
         </is>
@@ -1439,25 +1490,30 @@
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="n">
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>sem CC</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="n">
         <v>2649</v>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.10</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>Bens de Pequeno Valor</t>
         </is>
       </c>
-      <c r="O11" s="9" t="inlineStr">
+      <c r="P11" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>Compra AC (sem categoria gerencial no extrato): bem de pequeno valor/material. Confirmar.</t>
         </is>
@@ -1503,25 +1559,30 @@
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="n">
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>sem CC</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="n">
         <v>2649</v>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.10</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>Bens de Pequeno Valor</t>
         </is>
       </c>
-      <c r="O12" s="9" t="inlineStr">
+      <c r="P12" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>Compra AC (sem categoria gerencial no extrato): bem de pequeno valor/material. Confirmar.</t>
         </is>
@@ -1567,25 +1628,30 @@
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="4" t="n">
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>sem CC</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="n">
         <v>2649</v>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.10</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>Bens de Pequeno Valor</t>
         </is>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="P13" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P13" s="4" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>Compra AC (sem categoria gerencial no extrato): bem de pequeno valor/material. Confirmar.</t>
         </is>
@@ -1639,27 +1705,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="n">
         <v>2698</v>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>3.1.3.3.1.1</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>Despesas Bancarias</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P14" s="4" t="inlineStr">
-        <is>
-          <t>Tarifa bancária.</t>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>Tarifa bancária. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -1711,25 +1782,30 @@
           <t>CC337</t>
         </is>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>Desenvolvimento (DES)</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="n">
         <v>2524</v>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>2.1.1.1.1.4</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>Ferias a Pagar</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
+      <c r="P15" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P15" s="4" t="inlineStr">
+      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>Pagamento de férias (2524 Férias a Pagar).</t>
         </is>
@@ -1783,27 +1859,32 @@
           <t>CC833</t>
         </is>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="n">
         <v>3133</v>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>3.1.3.1.2.1.28</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>Brindes/Presentes para Clientes</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P16" s="4" t="inlineStr">
-        <is>
-          <t>Brindes/presentes para clientes. Se for propaganda: 3060.</t>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>Brindes/presentes para clientes. Se for propaganda: 3060. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -1855,27 +1936,32 @@
           <t>CC744</t>
         </is>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="n">
         <v>3067</v>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.3</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiros (PJ)</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
+      <c r="P17" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr">
-        <is>
-          <t>Custo de serviço terceiro (PJ).</t>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>Custo de serviço terceiro (PJ). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -1927,27 +2013,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="n">
         <v>2436</v>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>1.1.2.1.1</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>Clientes a Receber</t>
         </is>
       </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P18" s="4" t="inlineStr">
-        <is>
-          <t>Baixa de duplicata/mensalidade de cliente.</t>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>Recebimento de cliente (baixa de duplicata/mensalidade). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -1999,27 +2090,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="n">
         <v>2687</v>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.48</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>Despesas Diversas</t>
         </is>
       </c>
-      <c r="O19" s="9" t="inlineStr">
+      <c r="P19" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P19" s="4" t="inlineStr">
-        <is>
-          <t>Cartão Paytrack (despesas de viagem/combustível). Conferir prestação de contas; recarga pode ser adiantamento (2464).</t>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>Cartão Paytrack (despesas de viagem/combustível). Conferir prestação de contas; recarga pode ser adiantamento (2464). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -2067,27 +2163,32 @@
           <t>CC318</t>
         </is>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="n">
         <v>2872</v>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>1.1.1.2.5</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>Transferência de recursos</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P20" s="4" t="inlineStr">
-        <is>
-          <t>Transferência entre Matriz e Filial. Confirmar se o escritório usa 2872 (Transferência de recursos) ou mútuo (3086/2861).</t>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>Transferência entre Matriz e Filial. Confirmar se o escritório usa 2872 (Transferência de recursos) ou mútuo (3086/2861). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -2135,27 +2236,32 @@
           <t>CC318</t>
         </is>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="n">
         <v>2872</v>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>1.1.1.2.5</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>Transferência de recursos</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
+      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P21" s="4" t="inlineStr">
-        <is>
-          <t>Transferência entre Matriz e Filial. Confirmar se o escritório usa 2872 (Transferência de recursos) ou mútuo (3086/2861).</t>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>Transferência entre Matriz e Filial. Confirmar se o escritório usa 2872 (Transferência de recursos) ou mútuo (3086/2861). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -2207,27 +2313,32 @@
           <t>CC833</t>
         </is>
       </c>
-      <c r="L22" s="4" t="n">
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="n">
         <v>2658</v>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.19</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>Fretes, Carretos e Motoboy</t>
         </is>
       </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P22" s="4" t="inlineStr">
-        <is>
-          <t>Frete/motoboy.</t>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>Frete/motoboy. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -2279,27 +2390,32 @@
           <t>CC318</t>
         </is>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="n">
         <v>3085</v>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>2.1.1.3.4</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>Empréstimo de Mútuo DCK</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
+      <c r="P23" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P23" s="4" t="inlineStr">
-        <is>
-          <t>Empréstimo/mútuo recebido da DCK. Alternativa: 2861 (DCK/KORP Intercompany).</t>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>Empréstimo/mútuo recebido da DCK. Alternativa: 2861 (DCK/KORP Intercompany). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -2351,27 +2467,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L24" s="4" t="n">
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="n">
         <v>2859</v>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.4</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>Licenciamento, Manutenção e Assinaturas Softwares Terceiros</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
+      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P24" s="4" t="inlineStr">
-        <is>
-          <t>Licenciamento/manutenção de software de terceiros. Alternativa (custo de serviço): 2839.</t>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>Licenciamento/manutenção de software de terceiros. Alternativa (custo de serviço): 2839. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -2423,27 +2544,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L25" s="4" t="n">
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="n">
         <v>2859</v>
       </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.4</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>Licenciamento, Manutenção e Assinaturas Softwares Terceiros</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
+      <c r="P25" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P25" s="4" t="inlineStr">
-        <is>
-          <t>Licenciamento/manutenção de software de terceiros. Alternativa (custo de serviço): 2839.</t>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>Licenciamento/manutenção de software de terceiros. Alternativa (custo de serviço): 2839. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -2495,27 +2621,32 @@
           <t>CC318</t>
         </is>
       </c>
-      <c r="L26" s="4" t="n">
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="n">
         <v>2698</v>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>3.1.3.3.1.1</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>Despesas Bancarias</t>
         </is>
       </c>
-      <c r="O26" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P26" s="4" t="inlineStr">
-        <is>
-          <t>Tarifa bancária.</t>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>Tarifa bancária. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -2567,27 +2698,32 @@
           <t>CC344</t>
         </is>
       </c>
-      <c r="L27" s="4" t="n">
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="n">
         <v>2523</v>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>2.1.1.1.1.3</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>Indenizacoes Trabalhistas</t>
         </is>
       </c>
-      <c r="O27" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P27" s="4" t="inlineStr">
-        <is>
-          <t>Rescisão (padrão da folha Korp: 2523 Indenizações Trabalhistas).</t>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>Rescisão (padrão da folha Korp: 2523 Indenizações Trabalhistas). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -2639,27 +2775,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="n">
         <v>2529</v>
       </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>2.1.1.1.2.1</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>Contrib. Sindical a Recolher</t>
         </is>
       </c>
-      <c r="O28" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P28" s="4" t="inlineStr">
-        <is>
-          <t>Contribuição sindical a recolher.</t>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>Contribuição sindical a recolher. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -2711,25 +2852,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="n">
         <v>2869</v>
       </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.59</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>Despesas com Condomínio</t>
         </is>
       </c>
-      <c r="O29" s="7" t="inlineStr">
+      <c r="P29" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P29" s="4" t="inlineStr">
+      <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>Condomínio.</t>
         </is>
@@ -2783,25 +2929,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="n">
         <v>2869</v>
       </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.59</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>Despesas com Condomínio</t>
         </is>
       </c>
-      <c r="O30" s="7" t="inlineStr">
+      <c r="P30" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P30" s="4" t="inlineStr">
+      <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>Condomínio.</t>
         </is>
@@ -2855,25 +3006,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="n">
         <v>2869</v>
       </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.59</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>Despesas com Condomínio</t>
         </is>
       </c>
-      <c r="O31" s="7" t="inlineStr">
+      <c r="P31" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P31" s="4" t="inlineStr">
+      <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>Condomínio.</t>
         </is>
@@ -2927,25 +3083,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L32" s="4" t="n">
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="n">
         <v>2869</v>
       </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="N32" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.59</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>Despesas com Condomínio</t>
         </is>
       </c>
-      <c r="O32" s="7" t="inlineStr">
+      <c r="P32" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P32" s="4" t="inlineStr">
+      <c r="Q32" s="4" t="inlineStr">
         <is>
           <t>Condomínio.</t>
         </is>
@@ -2999,27 +3160,32 @@
           <t>CC833</t>
         </is>
       </c>
-      <c r="L33" s="4" t="n">
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="n">
         <v>3067</v>
       </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.3</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiros (PJ)</t>
         </is>
       </c>
-      <c r="O33" s="9" t="inlineStr">
+      <c r="P33" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P33" s="4" t="inlineStr">
-        <is>
-          <t>Mesmo fornecedor/categoria RSV Transf. Digital: confirmar natureza.</t>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>Mesmo fornecedor/categoria RSV Transf. Digital: confirmar natureza. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -3071,25 +3237,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="n">
         <v>2661</v>
       </c>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.22</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>Informatica (Consertos e Pecas) Adm</t>
         </is>
       </c>
-      <c r="O34" s="9" t="inlineStr">
+      <c r="P34" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P34" s="4" t="inlineStr">
+      <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>Informática (infra/peças). Confirmar.</t>
         </is>
@@ -3143,27 +3314,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L35" s="4" t="n">
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="n">
         <v>3046</v>
       </c>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>2.1.1.1.5.6</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="O35" s="4" t="inlineStr">
         <is>
           <t>Refeições</t>
         </is>
       </c>
-      <c r="O35" s="8" t="inlineStr">
+      <c r="P35" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P35" s="4" t="inlineStr">
-        <is>
-          <t>Vale-refeição/alimentação (Benefícios - Refeições). Alternativa: 3043 PAT.</t>
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>Vale-refeição/alimentação (Benefícios - Refeições). Alternativa: 3043 PAT. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -3215,27 +3391,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L36" s="4" t="n">
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="n">
         <v>2698</v>
       </c>
-      <c r="M36" s="4" t="inlineStr">
+      <c r="N36" s="4" t="inlineStr">
         <is>
           <t>3.1.3.3.1.1</t>
         </is>
       </c>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <t>Despesas Bancarias</t>
         </is>
       </c>
-      <c r="O36" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P36" s="4" t="inlineStr">
-        <is>
-          <t>Tarifa bancária.</t>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="inlineStr">
+        <is>
+          <t>Tarifa bancária. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -3287,25 +3468,30 @@
           <t>CC345</t>
         </is>
       </c>
-      <c r="L37" s="4" t="n">
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>Suporte</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="n">
         <v>2524</v>
       </c>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="N37" s="4" t="inlineStr">
         <is>
           <t>2.1.1.1.1.4</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="O37" s="4" t="inlineStr">
         <is>
           <t>Ferias a Pagar</t>
         </is>
       </c>
-      <c r="O37" s="7" t="inlineStr">
+      <c r="P37" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P37" s="4" t="inlineStr">
+      <c r="Q37" s="4" t="inlineStr">
         <is>
           <t>Pagamento de férias (2524 Férias a Pagar).</t>
         </is>
@@ -3359,27 +3545,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L38" s="4" t="n">
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="n">
         <v>2436</v>
       </c>
-      <c r="M38" s="4" t="inlineStr">
+      <c r="N38" s="4" t="inlineStr">
         <is>
           <t>1.1.2.1.1</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>Clientes a Receber</t>
         </is>
       </c>
-      <c r="O38" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P38" s="4" t="inlineStr">
-        <is>
-          <t>Baixa de duplicata/mensalidade de cliente.</t>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t>Recebimento de cliente (baixa de duplicata/mensalidade). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -3431,27 +3622,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L39" s="4" t="n">
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="n">
         <v>2436</v>
       </c>
-      <c r="M39" s="4" t="inlineStr">
+      <c r="N39" s="4" t="inlineStr">
         <is>
           <t>1.1.2.1.1</t>
         </is>
       </c>
-      <c r="N39" s="4" t="inlineStr">
+      <c r="O39" s="4" t="inlineStr">
         <is>
           <t>Clientes a Receber</t>
         </is>
       </c>
-      <c r="O39" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P39" s="4" t="inlineStr">
-        <is>
-          <t>Baixa de duplicata/mensalidade de cliente.</t>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
+        <is>
+          <t>Recebimento de cliente (baixa de duplicata/mensalidade). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -3499,27 +3695,32 @@
           <t>CC318</t>
         </is>
       </c>
-      <c r="L40" s="4" t="n">
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="n">
         <v>2872</v>
       </c>
-      <c r="M40" s="4" t="inlineStr">
+      <c r="N40" s="4" t="inlineStr">
         <is>
           <t>1.1.1.2.5</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>Transferência de recursos</t>
         </is>
       </c>
-      <c r="O40" s="8" t="inlineStr">
+      <c r="P40" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P40" s="4" t="inlineStr">
-        <is>
-          <t>Transferência entre Matriz e Filial. Confirmar se o escritório usa 2872 (Transferência de recursos) ou mútuo (3086/2861).</t>
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>Transferência entre Matriz e Filial. Confirmar se o escritório usa 2872 (Transferência de recursos) ou mútuo (3086/2861). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -3571,25 +3772,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="n">
         <v>2688</v>
       </c>
-      <c r="M41" s="4" t="inlineStr">
+      <c r="N41" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.49</t>
         </is>
       </c>
-      <c r="N41" s="4" t="inlineStr">
+      <c r="O41" s="4" t="inlineStr">
         <is>
           <t>Energia Eletrica</t>
         </is>
       </c>
-      <c r="O41" s="7" t="inlineStr">
+      <c r="P41" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P41" s="4" t="inlineStr">
+      <c r="Q41" s="4" t="inlineStr">
         <is>
           <t>Energia elétrica.</t>
         </is>
@@ -3643,25 +3849,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L42" s="4" t="n">
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="n">
         <v>2688</v>
       </c>
-      <c r="M42" s="4" t="inlineStr">
+      <c r="N42" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.49</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>Energia Eletrica</t>
         </is>
       </c>
-      <c r="O42" s="7" t="inlineStr">
+      <c r="P42" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P42" s="4" t="inlineStr">
+      <c r="Q42" s="4" t="inlineStr">
         <is>
           <t>Energia elétrica.</t>
         </is>
@@ -3715,27 +3926,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L43" s="4" t="n">
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="n">
         <v>2859</v>
       </c>
-      <c r="M43" s="4" t="inlineStr">
+      <c r="N43" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.4</t>
         </is>
       </c>
-      <c r="N43" s="4" t="inlineStr">
+      <c r="O43" s="4" t="inlineStr">
         <is>
           <t>Licenciamento, Manutenção e Assinaturas Softwares Terceiros</t>
         </is>
       </c>
-      <c r="O43" s="8" t="inlineStr">
+      <c r="P43" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P43" s="4" t="inlineStr">
-        <is>
-          <t>Licenciamento/manutenção de software de terceiros. Alternativa (custo de serviço): 2839.</t>
+      <c r="Q43" s="4" t="inlineStr">
+        <is>
+          <t>Licenciamento/manutenção de software de terceiros. Alternativa (custo de serviço): 2839. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -3787,25 +4003,30 @@
           <t>CC644</t>
         </is>
       </c>
-      <c r="L44" s="4" t="n">
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>Consultoria / CS</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="n">
         <v>3065</v>
       </c>
-      <c r="M44" s="4" t="inlineStr">
+      <c r="N44" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.1</t>
         </is>
       </c>
-      <c r="N44" s="4" t="inlineStr">
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Consultores)</t>
         </is>
       </c>
-      <c r="O44" s="7" t="inlineStr">
+      <c r="P44" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P44" s="4" t="inlineStr">
+      <c r="Q44" s="4" t="inlineStr">
         <is>
           <t>Custo de serviço terceiro - Consultores.</t>
         </is>
@@ -3859,25 +4080,30 @@
           <t>CC506</t>
         </is>
       </c>
-      <c r="L45" s="4" t="n">
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>Qualidade</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="n">
         <v>3138</v>
       </c>
-      <c r="M45" s="4" t="inlineStr">
+      <c r="N45" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.5</t>
         </is>
       </c>
-      <c r="N45" s="4" t="inlineStr">
+      <c r="O45" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Qualidade)</t>
         </is>
       </c>
-      <c r="O45" s="7" t="inlineStr">
+      <c r="P45" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P45" s="4" t="inlineStr">
+      <c r="Q45" s="4" t="inlineStr">
         <is>
           <t>Custo de serviço terceiro - Qualidade.</t>
         </is>
@@ -3931,25 +4157,30 @@
           <t>CC337</t>
         </is>
       </c>
-      <c r="L46" s="4" t="n">
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>Desenvolvimento (DES)</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="n">
         <v>3139</v>
       </c>
-      <c r="M46" s="4" t="inlineStr">
+      <c r="N46" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.6</t>
         </is>
       </c>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Desenvolvedor)</t>
         </is>
       </c>
-      <c r="O46" s="7" t="inlineStr">
+      <c r="P46" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P46" s="4" t="inlineStr">
+      <c r="Q46" s="4" t="inlineStr">
         <is>
           <t>Custo de serviço terceiro - Desenvolvedor.</t>
         </is>
@@ -4003,25 +4234,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L47" s="4" t="n">
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="n">
         <v>2661</v>
       </c>
-      <c r="M47" s="4" t="inlineStr">
+      <c r="N47" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.22</t>
         </is>
       </c>
-      <c r="N47" s="4" t="inlineStr">
+      <c r="O47" s="4" t="inlineStr">
         <is>
           <t>Informatica (Consertos e Pecas) Adm</t>
         </is>
       </c>
-      <c r="O47" s="9" t="inlineStr">
+      <c r="P47" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P47" s="4" t="inlineStr">
+      <c r="Q47" s="4" t="inlineStr">
         <is>
           <t>Informática (infra/peças). Confirmar.</t>
         </is>
@@ -4075,27 +4311,32 @@
           <t>CC335</t>
         </is>
       </c>
-      <c r="L48" s="4" t="n">
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="n">
         <v>3139</v>
       </c>
-      <c r="M48" s="4" t="inlineStr">
+      <c r="N48" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.6</t>
         </is>
       </c>
-      <c r="N48" s="4" t="inlineStr">
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Desenvolvedor)</t>
         </is>
       </c>
-      <c r="O48" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P48" s="4" t="inlineStr">
-        <is>
-          <t>Custo de serviço terceiro - Desenvolvedor.</t>
+      <c r="P48" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q48" s="4" t="inlineStr">
+        <is>
+          <t>Custo de serviço terceiro - Desenvolvedor. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -4147,27 +4388,32 @@
           <t>CC833</t>
         </is>
       </c>
-      <c r="L49" s="4" t="n">
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="n">
         <v>3067</v>
       </c>
-      <c r="M49" s="4" t="inlineStr">
+      <c r="N49" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.3</t>
         </is>
       </c>
-      <c r="N49" s="4" t="inlineStr">
+      <c r="O49" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiros (PJ)</t>
         </is>
       </c>
-      <c r="O49" s="9" t="inlineStr">
+      <c r="P49" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P49" s="4" t="inlineStr">
-        <is>
-          <t>Categoria RSV Transf. Digital: confirmar natureza (custo de serviço PJ ou repasse).</t>
+      <c r="Q49" s="4" t="inlineStr">
+        <is>
+          <t>Categoria RSV Transf. Digital: confirmar natureza (custo de serviço PJ ou repasse). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -4219,25 +4465,30 @@
           <t>CC644</t>
         </is>
       </c>
-      <c r="L50" s="4" t="n">
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>Consultoria / CS</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="n">
         <v>3065</v>
       </c>
-      <c r="M50" s="4" t="inlineStr">
+      <c r="N50" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.1</t>
         </is>
       </c>
-      <c r="N50" s="4" t="inlineStr">
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Consultores)</t>
         </is>
       </c>
-      <c r="O50" s="7" t="inlineStr">
+      <c r="P50" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P50" s="4" t="inlineStr">
+      <c r="Q50" s="4" t="inlineStr">
         <is>
           <t>Custo de serviço terceiro - Consultores.</t>
         </is>
@@ -4291,27 +4542,32 @@
           <t>CC773</t>
         </is>
       </c>
-      <c r="L51" s="4" t="n">
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="n">
         <v>3141</v>
       </c>
-      <c r="M51" s="4" t="inlineStr">
+      <c r="N51" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.8</t>
         </is>
       </c>
-      <c r="N51" s="4" t="inlineStr">
+      <c r="O51" s="4" t="inlineStr">
         <is>
           <t>Custo Serviços Terceiros (PJ Comercial)</t>
         </is>
       </c>
-      <c r="O51" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P51" s="4" t="inlineStr">
-        <is>
-          <t>Custo de serviço terceiro - PJ Comercial.</t>
+      <c r="P51" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="inlineStr">
+        <is>
+          <t>Custo de serviço terceiro - PJ Comercial. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -4363,27 +4619,32 @@
           <t>CC831</t>
         </is>
       </c>
-      <c r="L52" s="4" t="n">
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M52" s="4" t="n">
         <v>3141</v>
       </c>
-      <c r="M52" s="4" t="inlineStr">
+      <c r="N52" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.8</t>
         </is>
       </c>
-      <c r="N52" s="4" t="inlineStr">
+      <c r="O52" s="4" t="inlineStr">
         <is>
           <t>Custo Serviços Terceiros (PJ Comercial)</t>
         </is>
       </c>
-      <c r="O52" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P52" s="4" t="inlineStr">
-        <is>
-          <t>Custo de serviço terceiro - PJ Comercial.</t>
+      <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q52" s="4" t="inlineStr">
+        <is>
+          <t>Custo de serviço terceiro - PJ Comercial. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -4435,27 +4696,32 @@
           <t>CC830</t>
         </is>
       </c>
-      <c r="L53" s="4" t="n">
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="n">
         <v>3141</v>
       </c>
-      <c r="M53" s="4" t="inlineStr">
+      <c r="N53" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.8</t>
         </is>
       </c>
-      <c r="N53" s="4" t="inlineStr">
+      <c r="O53" s="4" t="inlineStr">
         <is>
           <t>Custo Serviços Terceiros (PJ Comercial)</t>
         </is>
       </c>
-      <c r="O53" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P53" s="4" t="inlineStr">
-        <is>
-          <t>Custo de serviço terceiro - PJ Comercial.</t>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q53" s="4" t="inlineStr">
+        <is>
+          <t>Custo de serviço terceiro - PJ Comercial. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -4507,27 +4773,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L54" s="4" t="n">
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="n">
         <v>2687</v>
       </c>
-      <c r="M54" s="4" t="inlineStr">
+      <c r="N54" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.48</t>
         </is>
       </c>
-      <c r="N54" s="4" t="inlineStr">
+      <c r="O54" s="4" t="inlineStr">
         <is>
           <t>Despesas Diversas</t>
         </is>
       </c>
-      <c r="O54" s="9" t="inlineStr">
+      <c r="P54" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P54" s="4" t="inlineStr">
-        <is>
-          <t>Cartão Paytrack (despesas de viagem/combustível). Conferir prestação de contas; recarga pode ser adiantamento (2464).</t>
+      <c r="Q54" s="4" t="inlineStr">
+        <is>
+          <t>Cartão Paytrack (despesas de viagem/combustível). Conferir prestação de contas; recarga pode ser adiantamento (2464). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -4571,25 +4842,30 @@
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr"/>
-      <c r="L55" s="4" t="n">
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>sem CC</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="n">
         <v>2649</v>
       </c>
-      <c r="M55" s="4" t="inlineStr">
+      <c r="N55" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.10</t>
         </is>
       </c>
-      <c r="N55" s="4" t="inlineStr">
+      <c r="O55" s="4" t="inlineStr">
         <is>
           <t>Bens de Pequeno Valor</t>
         </is>
       </c>
-      <c r="O55" s="9" t="inlineStr">
+      <c r="P55" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P55" s="4" t="inlineStr">
+      <c r="Q55" s="4" t="inlineStr">
         <is>
           <t>Compra AC (sem categoria gerencial no extrato): bem de pequeno valor/material. Confirmar.</t>
         </is>
@@ -4635,25 +4911,30 @@
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr"/>
-      <c r="L56" s="4" t="n">
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>sem CC</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="n">
         <v>2649</v>
       </c>
-      <c r="M56" s="4" t="inlineStr">
+      <c r="N56" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.10</t>
         </is>
       </c>
-      <c r="N56" s="4" t="inlineStr">
+      <c r="O56" s="4" t="inlineStr">
         <is>
           <t>Bens de Pequeno Valor</t>
         </is>
       </c>
-      <c r="O56" s="9" t="inlineStr">
+      <c r="P56" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P56" s="4" t="inlineStr">
+      <c r="Q56" s="4" t="inlineStr">
         <is>
           <t>Compra AC (sem categoria gerencial no extrato): bem de pequeno valor/material. Confirmar.</t>
         </is>
@@ -4699,25 +4980,30 @@
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr"/>
-      <c r="L57" s="4" t="n">
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>sem CC</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="n">
         <v>2649</v>
       </c>
-      <c r="M57" s="4" t="inlineStr">
+      <c r="N57" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.10</t>
         </is>
       </c>
-      <c r="N57" s="4" t="inlineStr">
+      <c r="O57" s="4" t="inlineStr">
         <is>
           <t>Bens de Pequeno Valor</t>
         </is>
       </c>
-      <c r="O57" s="9" t="inlineStr">
+      <c r="P57" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P57" s="4" t="inlineStr">
+      <c r="Q57" s="4" t="inlineStr">
         <is>
           <t>Compra AC (sem categoria gerencial no extrato): bem de pequeno valor/material. Confirmar.</t>
         </is>
@@ -4763,25 +5049,30 @@
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr"/>
-      <c r="L58" s="4" t="n">
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>sem CC</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="n">
         <v>2649</v>
       </c>
-      <c r="M58" s="4" t="inlineStr">
+      <c r="N58" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.10</t>
         </is>
       </c>
-      <c r="N58" s="4" t="inlineStr">
+      <c r="O58" s="4" t="inlineStr">
         <is>
           <t>Bens de Pequeno Valor</t>
         </is>
       </c>
-      <c r="O58" s="9" t="inlineStr">
+      <c r="P58" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P58" s="4" t="inlineStr">
+      <c r="Q58" s="4" t="inlineStr">
         <is>
           <t>Compra AC (sem categoria gerencial no extrato): bem de pequeno valor/material. Confirmar.</t>
         </is>
@@ -4835,27 +5126,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L59" s="4" t="n">
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="n">
         <v>3107</v>
       </c>
-      <c r="M59" s="4" t="inlineStr">
+      <c r="N59" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.1.17.8.14</t>
         </is>
       </c>
-      <c r="N59" s="4" t="inlineStr">
+      <c r="O59" s="4" t="inlineStr">
         <is>
           <t>Saúde Ocupacional</t>
         </is>
       </c>
-      <c r="O59" s="8" t="inlineStr">
+      <c r="P59" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P59" s="4" t="inlineStr">
-        <is>
-          <t>Exames ocupacionais. Se for admissional/demissional/periódico, usar 3038/3039/3069.</t>
+      <c r="Q59" s="4" t="inlineStr">
+        <is>
+          <t>Exames ocupacionais. Se for admissional/demissional/periódico, usar 3038/3039/3069. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -4907,27 +5203,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L60" s="4" t="n">
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="n">
         <v>3107</v>
       </c>
-      <c r="M60" s="4" t="inlineStr">
+      <c r="N60" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.1.17.8.14</t>
         </is>
       </c>
-      <c r="N60" s="4" t="inlineStr">
+      <c r="O60" s="4" t="inlineStr">
         <is>
           <t>Saúde Ocupacional</t>
         </is>
       </c>
-      <c r="O60" s="8" t="inlineStr">
+      <c r="P60" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P60" s="4" t="inlineStr">
-        <is>
-          <t>Exames ocupacionais. Se for admissional/demissional/periódico, usar 3038/3039/3069.</t>
+      <c r="Q60" s="4" t="inlineStr">
+        <is>
+          <t>Exames ocupacionais. Se for admissional/demissional/periódico, usar 3038/3039/3069. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -4979,27 +5280,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L61" s="4" t="n">
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="n">
         <v>3107</v>
       </c>
-      <c r="M61" s="4" t="inlineStr">
+      <c r="N61" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.1.17.8.14</t>
         </is>
       </c>
-      <c r="N61" s="4" t="inlineStr">
+      <c r="O61" s="4" t="inlineStr">
         <is>
           <t>Saúde Ocupacional</t>
         </is>
       </c>
-      <c r="O61" s="8" t="inlineStr">
+      <c r="P61" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P61" s="4" t="inlineStr">
-        <is>
-          <t>Exames ocupacionais. Se for admissional/demissional/periódico, usar 3038/3039/3069.</t>
+      <c r="Q61" s="4" t="inlineStr">
+        <is>
+          <t>Exames ocupacionais. Se for admissional/demissional/periódico, usar 3038/3039/3069. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -5051,27 +5357,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L62" s="4" t="n">
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M62" s="4" t="n">
         <v>3107</v>
       </c>
-      <c r="M62" s="4" t="inlineStr">
+      <c r="N62" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.1.17.8.14</t>
         </is>
       </c>
-      <c r="N62" s="4" t="inlineStr">
+      <c r="O62" s="4" t="inlineStr">
         <is>
           <t>Saúde Ocupacional</t>
         </is>
       </c>
-      <c r="O62" s="8" t="inlineStr">
+      <c r="P62" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P62" s="4" t="inlineStr">
-        <is>
-          <t>Exames ocupacionais. Se for admissional/demissional/periódico, usar 3038/3039/3069.</t>
+      <c r="Q62" s="4" t="inlineStr">
+        <is>
+          <t>Exames ocupacionais. Se for admissional/demissional/periódico, usar 3038/3039/3069. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -5123,25 +5434,30 @@
           <t>CC337</t>
         </is>
       </c>
-      <c r="L63" s="4" t="n">
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>Desenvolvimento (DES)</t>
+        </is>
+      </c>
+      <c r="M63" s="4" t="n">
         <v>3139</v>
       </c>
-      <c r="M63" s="4" t="inlineStr">
+      <c r="N63" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.6</t>
         </is>
       </c>
-      <c r="N63" s="4" t="inlineStr">
+      <c r="O63" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Desenvolvedor)</t>
         </is>
       </c>
-      <c r="O63" s="7" t="inlineStr">
+      <c r="P63" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P63" s="4" t="inlineStr">
+      <c r="Q63" s="4" t="inlineStr">
         <is>
           <t>Custo de serviço terceiro - Desenvolvedor.</t>
         </is>
@@ -5195,25 +5511,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L64" s="4" t="n">
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M64" s="4" t="n">
         <v>2629</v>
       </c>
-      <c r="M64" s="4" t="inlineStr">
+      <c r="N64" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.2.1.2</t>
         </is>
       </c>
-      <c r="N64" s="4" t="inlineStr">
+      <c r="O64" s="4" t="inlineStr">
         <is>
           <t>Honorarios Advocaticios</t>
         </is>
       </c>
-      <c r="O64" s="7" t="inlineStr">
+      <c r="P64" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P64" s="4" t="inlineStr">
+      <c r="Q64" s="4" t="inlineStr">
         <is>
           <t>Honorários advocatícios.</t>
         </is>
@@ -5267,27 +5588,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L65" s="4" t="n">
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M65" s="4" t="n">
         <v>2859</v>
       </c>
-      <c r="M65" s="4" t="inlineStr">
+      <c r="N65" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.4</t>
         </is>
       </c>
-      <c r="N65" s="4" t="inlineStr">
+      <c r="O65" s="4" t="inlineStr">
         <is>
           <t>Licenciamento, Manutenção e Assinaturas Softwares Terceiros</t>
         </is>
       </c>
-      <c r="O65" s="8" t="inlineStr">
+      <c r="P65" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P65" s="4" t="inlineStr">
-        <is>
-          <t>Licenciamento/manutenção de software de terceiros. Alternativa (custo de serviço): 2839.</t>
+      <c r="Q65" s="4" t="inlineStr">
+        <is>
+          <t>Licenciamento/manutenção de software de terceiros. Alternativa (custo de serviço): 2839. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -5339,27 +5665,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L66" s="4" t="n">
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M66" s="4" t="n">
         <v>2859</v>
       </c>
-      <c r="M66" s="4" t="inlineStr">
+      <c r="N66" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.4</t>
         </is>
       </c>
-      <c r="N66" s="4" t="inlineStr">
+      <c r="O66" s="4" t="inlineStr">
         <is>
           <t>Licenciamento, Manutenção e Assinaturas Softwares Terceiros</t>
         </is>
       </c>
-      <c r="O66" s="8" t="inlineStr">
+      <c r="P66" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P66" s="4" t="inlineStr">
-        <is>
-          <t>Licenciamento/manutenção de software de terceiros. Alternativa (custo de serviço): 2839.</t>
+      <c r="Q66" s="4" t="inlineStr">
+        <is>
+          <t>Licenciamento/manutenção de software de terceiros. Alternativa (custo de serviço): 2839. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -5411,25 +5742,30 @@
           <t>CC337</t>
         </is>
       </c>
-      <c r="L67" s="4" t="n">
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>Desenvolvimento (DES)</t>
+        </is>
+      </c>
+      <c r="M67" s="4" t="n">
         <v>3139</v>
       </c>
-      <c r="M67" s="4" t="inlineStr">
+      <c r="N67" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.6</t>
         </is>
       </c>
-      <c r="N67" s="4" t="inlineStr">
+      <c r="O67" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Desenvolvedor)</t>
         </is>
       </c>
-      <c r="O67" s="7" t="inlineStr">
+      <c r="P67" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P67" s="4" t="inlineStr">
+      <c r="Q67" s="4" t="inlineStr">
         <is>
           <t>Custo de serviço terceiro - Desenvolvedor.</t>
         </is>
@@ -5483,25 +5819,30 @@
           <t>CC644</t>
         </is>
       </c>
-      <c r="L68" s="4" t="n">
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>Consultoria / CS</t>
+        </is>
+      </c>
+      <c r="M68" s="4" t="n">
         <v>3065</v>
       </c>
-      <c r="M68" s="4" t="inlineStr">
+      <c r="N68" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.1</t>
         </is>
       </c>
-      <c r="N68" s="4" t="inlineStr">
+      <c r="O68" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Consultores)</t>
         </is>
       </c>
-      <c r="O68" s="7" t="inlineStr">
+      <c r="P68" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P68" s="4" t="inlineStr">
+      <c r="Q68" s="4" t="inlineStr">
         <is>
           <t>Custo de serviço terceiro - Consultores.</t>
         </is>
@@ -5555,27 +5896,32 @@
           <t>CC335</t>
         </is>
       </c>
-      <c r="L69" s="4" t="n">
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M69" s="4" t="n">
         <v>3139</v>
       </c>
-      <c r="M69" s="4" t="inlineStr">
+      <c r="N69" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.6</t>
         </is>
       </c>
-      <c r="N69" s="4" t="inlineStr">
+      <c r="O69" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Desenvolvedor)</t>
         </is>
       </c>
-      <c r="O69" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P69" s="4" t="inlineStr">
-        <is>
-          <t>Custo de serviço terceiro - Desenvolvedor.</t>
+      <c r="P69" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q69" s="4" t="inlineStr">
+        <is>
+          <t>Custo de serviço terceiro - Desenvolvedor. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -5627,27 +5973,32 @@
           <t>CC314</t>
         </is>
       </c>
-      <c r="L70" s="4" t="n">
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M70" s="4" t="n">
         <v>3139</v>
       </c>
-      <c r="M70" s="4" t="inlineStr">
+      <c r="N70" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.6</t>
         </is>
       </c>
-      <c r="N70" s="4" t="inlineStr">
+      <c r="O70" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Desenvolvedor)</t>
         </is>
       </c>
-      <c r="O70" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P70" s="4" t="inlineStr">
-        <is>
-          <t>Custo de serviço terceiro - Desenvolvedor.</t>
+      <c r="P70" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q70" s="4" t="inlineStr">
+        <is>
+          <t>Custo de serviço terceiro - Desenvolvedor. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -5699,25 +6050,30 @@
           <t>CC644</t>
         </is>
       </c>
-      <c r="L71" s="4" t="n">
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>Consultoria / CS</t>
+        </is>
+      </c>
+      <c r="M71" s="4" t="n">
         <v>3065</v>
       </c>
-      <c r="M71" s="4" t="inlineStr">
+      <c r="N71" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.1</t>
         </is>
       </c>
-      <c r="N71" s="4" t="inlineStr">
+      <c r="O71" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Consultores)</t>
         </is>
       </c>
-      <c r="O71" s="7" t="inlineStr">
+      <c r="P71" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P71" s="4" t="inlineStr">
+      <c r="Q71" s="4" t="inlineStr">
         <is>
           <t>Custo de serviço terceiro - Consultores.</t>
         </is>
@@ -5771,25 +6127,30 @@
           <t>CC506</t>
         </is>
       </c>
-      <c r="L72" s="4" t="n">
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>Qualidade</t>
+        </is>
+      </c>
+      <c r="M72" s="4" t="n">
         <v>3138</v>
       </c>
-      <c r="M72" s="4" t="inlineStr">
+      <c r="N72" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.5</t>
         </is>
       </c>
-      <c r="N72" s="4" t="inlineStr">
+      <c r="O72" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Qualidade)</t>
         </is>
       </c>
-      <c r="O72" s="7" t="inlineStr">
+      <c r="P72" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P72" s="4" t="inlineStr">
+      <c r="Q72" s="4" t="inlineStr">
         <is>
           <t>Custo de serviço terceiro - Qualidade.</t>
         </is>
@@ -5843,27 +6204,32 @@
           <t>CC335</t>
         </is>
       </c>
-      <c r="L73" s="4" t="n">
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M73" s="4" t="n">
         <v>3139</v>
       </c>
-      <c r="M73" s="4" t="inlineStr">
+      <c r="N73" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.6</t>
         </is>
       </c>
-      <c r="N73" s="4" t="inlineStr">
+      <c r="O73" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Desenvolvedor)</t>
         </is>
       </c>
-      <c r="O73" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P73" s="4" t="inlineStr">
-        <is>
-          <t>Custo de serviço terceiro - Desenvolvedor.</t>
+      <c r="P73" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q73" s="4" t="inlineStr">
+        <is>
+          <t>Custo de serviço terceiro - Desenvolvedor. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -5915,27 +6281,32 @@
           <t>CC335</t>
         </is>
       </c>
-      <c r="L74" s="4" t="n">
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M74" s="4" t="n">
         <v>3139</v>
       </c>
-      <c r="M74" s="4" t="inlineStr">
+      <c r="N74" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.6</t>
         </is>
       </c>
-      <c r="N74" s="4" t="inlineStr">
+      <c r="O74" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Desenvolvedor)</t>
         </is>
       </c>
-      <c r="O74" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P74" s="4" t="inlineStr">
-        <is>
-          <t>Custo de serviço terceiro - Desenvolvedor.</t>
+      <c r="P74" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q74" s="4" t="inlineStr">
+        <is>
+          <t>Custo de serviço terceiro - Desenvolvedor. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -5987,25 +6358,30 @@
           <t>CC644</t>
         </is>
       </c>
-      <c r="L75" s="4" t="n">
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>Consultoria / CS</t>
+        </is>
+      </c>
+      <c r="M75" s="4" t="n">
         <v>3065</v>
       </c>
-      <c r="M75" s="4" t="inlineStr">
+      <c r="N75" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.1</t>
         </is>
       </c>
-      <c r="N75" s="4" t="inlineStr">
+      <c r="O75" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Consultores)</t>
         </is>
       </c>
-      <c r="O75" s="7" t="inlineStr">
+      <c r="P75" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P75" s="4" t="inlineStr">
+      <c r="Q75" s="4" t="inlineStr">
         <is>
           <t>Custo de serviço terceiro - Consultores.</t>
         </is>
@@ -6059,25 +6435,30 @@
           <t>CC506</t>
         </is>
       </c>
-      <c r="L76" s="4" t="n">
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>Qualidade</t>
+        </is>
+      </c>
+      <c r="M76" s="4" t="n">
         <v>3138</v>
       </c>
-      <c r="M76" s="4" t="inlineStr">
+      <c r="N76" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.5</t>
         </is>
       </c>
-      <c r="N76" s="4" t="inlineStr">
+      <c r="O76" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Qualidade)</t>
         </is>
       </c>
-      <c r="O76" s="7" t="inlineStr">
+      <c r="P76" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P76" s="4" t="inlineStr">
+      <c r="Q76" s="4" t="inlineStr">
         <is>
           <t>Custo de serviço terceiro - Qualidade.</t>
         </is>
@@ -6131,27 +6512,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L77" s="4" t="n">
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M77" s="4" t="n">
         <v>3113</v>
       </c>
-      <c r="M77" s="4" t="inlineStr">
+      <c r="N77" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.1.17.8.17</t>
         </is>
       </c>
-      <c r="N77" s="4" t="inlineStr">
+      <c r="O77" s="4" t="inlineStr">
         <is>
           <t>Recrutamento e Seleção</t>
         </is>
       </c>
-      <c r="O77" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P77" s="4" t="inlineStr">
-        <is>
-          <t>Recrutamento e seleção.</t>
+      <c r="P77" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q77" s="4" t="inlineStr">
+        <is>
+          <t>Recrutamento e seleção. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -6203,27 +6589,32 @@
           <t>CC616</t>
         </is>
       </c>
-      <c r="L78" s="4" t="n">
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M78" s="4" t="n">
         <v>2859</v>
       </c>
-      <c r="M78" s="4" t="inlineStr">
+      <c r="N78" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.4</t>
         </is>
       </c>
-      <c r="N78" s="4" t="inlineStr">
+      <c r="O78" s="4" t="inlineStr">
         <is>
           <t>Licenciamento, Manutenção e Assinaturas Softwares Terceiros</t>
         </is>
       </c>
-      <c r="O78" s="8" t="inlineStr">
+      <c r="P78" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P78" s="4" t="inlineStr">
-        <is>
-          <t>Licenciamento/manutenção de software de terceiros. Alternativa (custo de serviço): 2839.</t>
+      <c r="Q78" s="4" t="inlineStr">
+        <is>
+          <t>Licenciamento/manutenção de software de terceiros. Alternativa (custo de serviço): 2839. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -6275,25 +6666,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L79" s="4" t="n">
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M79" s="4" t="n">
         <v>3059</v>
       </c>
-      <c r="M79" s="4" t="inlineStr">
+      <c r="N79" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.61</t>
         </is>
       </c>
-      <c r="N79" s="4" t="inlineStr">
+      <c r="O79" s="4" t="inlineStr">
         <is>
           <t>Internet</t>
         </is>
       </c>
-      <c r="O79" s="8" t="inlineStr">
+      <c r="P79" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P79" s="4" t="inlineStr">
+      <c r="Q79" s="4" t="inlineStr">
         <is>
           <t>Internet/link dedicado. Telefonia: 2657.</t>
         </is>
@@ -6347,25 +6743,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L80" s="4" t="n">
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M80" s="4" t="n">
         <v>2657</v>
       </c>
-      <c r="M80" s="4" t="inlineStr">
+      <c r="N80" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.18</t>
         </is>
       </c>
-      <c r="N80" s="4" t="inlineStr">
+      <c r="O80" s="4" t="inlineStr">
         <is>
           <t>Comunicacao / Telefone (adm.)</t>
         </is>
       </c>
-      <c r="O80" s="7" t="inlineStr">
+      <c r="P80" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P80" s="4" t="inlineStr">
+      <c r="Q80" s="4" t="inlineStr">
         <is>
           <t>Telefone/comunicação.</t>
         </is>
@@ -6419,25 +6820,30 @@
           <t>CC345</t>
         </is>
       </c>
-      <c r="L81" s="4" t="n">
+      <c r="L81" s="4" t="inlineStr">
+        <is>
+          <t>Suporte</t>
+        </is>
+      </c>
+      <c r="M81" s="4" t="n">
         <v>2647</v>
       </c>
-      <c r="M81" s="4" t="inlineStr">
+      <c r="N81" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.8</t>
         </is>
       </c>
-      <c r="N81" s="4" t="inlineStr">
+      <c r="O81" s="4" t="inlineStr">
         <is>
           <t>Viagens</t>
         </is>
       </c>
-      <c r="O81" s="8" t="inlineStr">
+      <c r="P81" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P81" s="4" t="inlineStr">
+      <c r="Q81" s="4" t="inlineStr">
         <is>
           <t>Passagens/viagens. Se for comercial: 3034 ou 2587.</t>
         </is>
@@ -6491,27 +6897,32 @@
           <t>CC335</t>
         </is>
       </c>
-      <c r="L82" s="4" t="n">
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M82" s="4" t="n">
         <v>2647</v>
       </c>
-      <c r="M82" s="4" t="inlineStr">
+      <c r="N82" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.8</t>
         </is>
       </c>
-      <c r="N82" s="4" t="inlineStr">
+      <c r="O82" s="4" t="inlineStr">
         <is>
           <t>Viagens</t>
         </is>
       </c>
-      <c r="O82" s="8" t="inlineStr">
+      <c r="P82" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P82" s="4" t="inlineStr">
-        <is>
-          <t>Passagens/viagens. Se for comercial: 3034 ou 2587.</t>
+      <c r="Q82" s="4" t="inlineStr">
+        <is>
+          <t>Passagens/viagens. Se for comercial: 3034 ou 2587. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -6563,27 +6974,32 @@
           <t>CC335</t>
         </is>
       </c>
-      <c r="L83" s="4" t="n">
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M83" s="4" t="n">
         <v>2647</v>
       </c>
-      <c r="M83" s="4" t="inlineStr">
+      <c r="N83" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.8</t>
         </is>
       </c>
-      <c r="N83" s="4" t="inlineStr">
+      <c r="O83" s="4" t="inlineStr">
         <is>
           <t>Viagens</t>
         </is>
       </c>
-      <c r="O83" s="8" t="inlineStr">
+      <c r="P83" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P83" s="4" t="inlineStr">
-        <is>
-          <t>Passagens/viagens. Se for comercial: 3034 ou 2587.</t>
+      <c r="Q83" s="4" t="inlineStr">
+        <is>
+          <t>Passagens/viagens. Se for comercial: 3034 ou 2587. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -6635,27 +7051,32 @@
           <t>CC314</t>
         </is>
       </c>
-      <c r="L84" s="4" t="n">
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M84" s="4" t="n">
         <v>2647</v>
       </c>
-      <c r="M84" s="4" t="inlineStr">
+      <c r="N84" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.8</t>
         </is>
       </c>
-      <c r="N84" s="4" t="inlineStr">
+      <c r="O84" s="4" t="inlineStr">
         <is>
           <t>Viagens</t>
         </is>
       </c>
-      <c r="O84" s="8" t="inlineStr">
+      <c r="P84" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P84" s="4" t="inlineStr">
-        <is>
-          <t>Passagens/viagens. Se for comercial: 3034 ou 2587.</t>
+      <c r="Q84" s="4" t="inlineStr">
+        <is>
+          <t>Passagens/viagens. Se for comercial: 3034 ou 2587. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -6707,27 +7128,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L85" s="4" t="n">
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M85" s="4" t="n">
         <v>2859</v>
       </c>
-      <c r="M85" s="4" t="inlineStr">
+      <c r="N85" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.4</t>
         </is>
       </c>
-      <c r="N85" s="4" t="inlineStr">
+      <c r="O85" s="4" t="inlineStr">
         <is>
           <t>Licenciamento, Manutenção e Assinaturas Softwares Terceiros</t>
         </is>
       </c>
-      <c r="O85" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P85" s="4" t="inlineStr">
-        <is>
-          <t>Assinatura/licença de software.</t>
+      <c r="P85" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q85" s="4" t="inlineStr">
+        <is>
+          <t>Assinatura/licença de software. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -6779,27 +7205,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L86" s="4" t="n">
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M86" s="4" t="n">
         <v>2859</v>
       </c>
-      <c r="M86" s="4" t="inlineStr">
+      <c r="N86" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.4</t>
         </is>
       </c>
-      <c r="N86" s="4" t="inlineStr">
+      <c r="O86" s="4" t="inlineStr">
         <is>
           <t>Licenciamento, Manutenção e Assinaturas Softwares Terceiros</t>
         </is>
       </c>
-      <c r="O86" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P86" s="4" t="inlineStr">
-        <is>
-          <t>Assinatura/licença de software.</t>
+      <c r="P86" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q86" s="4" t="inlineStr">
+        <is>
+          <t>Assinatura/licença de software. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -6851,27 +7282,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L87" s="4" t="n">
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M87" s="4" t="n">
         <v>2859</v>
       </c>
-      <c r="M87" s="4" t="inlineStr">
+      <c r="N87" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.4</t>
         </is>
       </c>
-      <c r="N87" s="4" t="inlineStr">
+      <c r="O87" s="4" t="inlineStr">
         <is>
           <t>Licenciamento, Manutenção e Assinaturas Softwares Terceiros</t>
         </is>
       </c>
-      <c r="O87" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P87" s="4" t="inlineStr">
-        <is>
-          <t>Assinatura/licença de software.</t>
+      <c r="P87" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q87" s="4" t="inlineStr">
+        <is>
+          <t>Assinatura/licença de software. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -6923,27 +7359,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L88" s="4" t="n">
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M88" s="4" t="n">
         <v>2680</v>
       </c>
-      <c r="M88" s="4" t="inlineStr">
+      <c r="N88" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.41</t>
         </is>
       </c>
-      <c r="N88" s="4" t="inlineStr">
+      <c r="O88" s="4" t="inlineStr">
         <is>
           <t>Taxi</t>
         </is>
       </c>
-      <c r="O88" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P88" s="4" t="inlineStr">
-        <is>
-          <t>Transporte por aplicativo.</t>
+      <c r="P88" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q88" s="4" t="inlineStr">
+        <is>
+          <t>Transporte por aplicativo. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -6995,27 +7436,32 @@
           <t>CC318</t>
         </is>
       </c>
-      <c r="L89" s="4" t="n">
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M89" s="4" t="n">
         <v>2698</v>
       </c>
-      <c r="M89" s="4" t="inlineStr">
+      <c r="N89" s="4" t="inlineStr">
         <is>
           <t>3.1.3.3.1.1</t>
         </is>
       </c>
-      <c r="N89" s="4" t="inlineStr">
+      <c r="O89" s="4" t="inlineStr">
         <is>
           <t>Despesas Bancarias</t>
         </is>
       </c>
-      <c r="O89" s="8" t="inlineStr">
+      <c r="P89" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P89" s="4" t="inlineStr">
-        <is>
-          <t>IOF do cartão Sicredi (não há conta específica de IOF sobre compras).</t>
+      <c r="Q89" s="4" t="inlineStr">
+        <is>
+          <t>IOF do cartão Sicredi (não há conta específica de IOF sobre compras). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -7067,27 +7513,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L90" s="4" t="n">
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M90" s="4" t="n">
         <v>2859</v>
       </c>
-      <c r="M90" s="4" t="inlineStr">
+      <c r="N90" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.4</t>
         </is>
       </c>
-      <c r="N90" s="4" t="inlineStr">
+      <c r="O90" s="4" t="inlineStr">
         <is>
           <t>Licenciamento, Manutenção e Assinaturas Softwares Terceiros</t>
         </is>
       </c>
-      <c r="O90" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P90" s="4" t="inlineStr">
-        <is>
-          <t>Assinatura/licença de software.</t>
+      <c r="P90" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q90" s="4" t="inlineStr">
+        <is>
+          <t>Assinatura/licença de software. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -7139,27 +7590,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L91" s="4" t="n">
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M91" s="4" t="n">
         <v>2859</v>
       </c>
-      <c r="M91" s="4" t="inlineStr">
+      <c r="N91" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.4</t>
         </is>
       </c>
-      <c r="N91" s="4" t="inlineStr">
+      <c r="O91" s="4" t="inlineStr">
         <is>
           <t>Licenciamento, Manutenção e Assinaturas Softwares Terceiros</t>
         </is>
       </c>
-      <c r="O91" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P91" s="4" t="inlineStr">
-        <is>
-          <t>Assinatura/licença de software.</t>
+      <c r="P91" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q91" s="4" t="inlineStr">
+        <is>
+          <t>Assinatura/licença de software. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -7211,27 +7667,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L92" s="4" t="n">
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M92" s="4" t="n">
         <v>2859</v>
       </c>
-      <c r="M92" s="4" t="inlineStr">
+      <c r="N92" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.4</t>
         </is>
       </c>
-      <c r="N92" s="4" t="inlineStr">
+      <c r="O92" s="4" t="inlineStr">
         <is>
           <t>Licenciamento, Manutenção e Assinaturas Softwares Terceiros</t>
         </is>
       </c>
-      <c r="O92" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P92" s="4" t="inlineStr">
-        <is>
-          <t>Assinatura/licença de software.</t>
+      <c r="P92" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q92" s="4" t="inlineStr">
+        <is>
+          <t>Assinatura/licença de software. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -7283,27 +7744,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L93" s="4" t="n">
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M93" s="4" t="n">
         <v>2859</v>
       </c>
-      <c r="M93" s="4" t="inlineStr">
+      <c r="N93" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.4</t>
         </is>
       </c>
-      <c r="N93" s="4" t="inlineStr">
+      <c r="O93" s="4" t="inlineStr">
         <is>
           <t>Licenciamento, Manutenção e Assinaturas Softwares Terceiros</t>
         </is>
       </c>
-      <c r="O93" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P93" s="4" t="inlineStr">
-        <is>
-          <t>Assinatura/licença de software.</t>
+      <c r="P93" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q93" s="4" t="inlineStr">
+        <is>
+          <t>Assinatura/licença de software. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -7355,27 +7821,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L94" s="4" t="n">
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M94" s="4" t="n">
         <v>2859</v>
       </c>
-      <c r="M94" s="4" t="inlineStr">
+      <c r="N94" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.4</t>
         </is>
       </c>
-      <c r="N94" s="4" t="inlineStr">
+      <c r="O94" s="4" t="inlineStr">
         <is>
           <t>Licenciamento, Manutenção e Assinaturas Softwares Terceiros</t>
         </is>
       </c>
-      <c r="O94" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P94" s="4" t="inlineStr">
-        <is>
-          <t>Assinatura/licença de software.</t>
+      <c r="P94" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q94" s="4" t="inlineStr">
+        <is>
+          <t>Assinatura/licença de software. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -7427,27 +7898,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L95" s="4" t="n">
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M95" s="4" t="n">
         <v>2859</v>
       </c>
-      <c r="M95" s="4" t="inlineStr">
+      <c r="N95" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.4</t>
         </is>
       </c>
-      <c r="N95" s="4" t="inlineStr">
+      <c r="O95" s="4" t="inlineStr">
         <is>
           <t>Licenciamento, Manutenção e Assinaturas Softwares Terceiros</t>
         </is>
       </c>
-      <c r="O95" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P95" s="4" t="inlineStr">
-        <is>
-          <t>Assinatura/licença de software.</t>
+      <c r="P95" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q95" s="4" t="inlineStr">
+        <is>
+          <t>Assinatura/licença de software. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -7499,27 +7975,32 @@
           <t>CC645</t>
         </is>
       </c>
-      <c r="L96" s="4" t="n">
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M96" s="4" t="n">
         <v>2524</v>
       </c>
-      <c r="M96" s="4" t="inlineStr">
+      <c r="N96" s="4" t="inlineStr">
         <is>
           <t>2.1.1.1.1.4</t>
         </is>
       </c>
-      <c r="N96" s="4" t="inlineStr">
+      <c r="O96" s="4" t="inlineStr">
         <is>
           <t>Ferias a Pagar</t>
         </is>
       </c>
-      <c r="O96" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P96" s="4" t="inlineStr">
-        <is>
-          <t>Pagamento de férias (2524 Férias a Pagar).</t>
+      <c r="P96" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q96" s="4" t="inlineStr">
+        <is>
+          <t>Pagamento de férias (2524 Férias a Pagar). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -7571,27 +8052,32 @@
           <t>CC314</t>
         </is>
       </c>
-      <c r="L97" s="4" t="n">
+      <c r="L97" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M97" s="4" t="n">
         <v>2587</v>
       </c>
-      <c r="M97" s="4" t="inlineStr">
+      <c r="N97" s="4" t="inlineStr">
         <is>
           <t>3.1.3.1.2.1.4</t>
         </is>
       </c>
-      <c r="N97" s="4" t="inlineStr">
+      <c r="O97" s="4" t="inlineStr">
         <is>
           <t>Despesas com Viagens/Hospedagem</t>
         </is>
       </c>
-      <c r="O97" s="8" t="inlineStr">
+      <c r="P97" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P97" s="4" t="inlineStr">
-        <is>
-          <t>Hospedagem (despesa comercial). Se for administrativa: 2647 Viagens.</t>
+      <c r="Q97" s="4" t="inlineStr">
+        <is>
+          <t>Hospedagem (despesa comercial). Se for administrativa: 2647 Viagens. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -7643,27 +8129,32 @@
           <t>CC744</t>
         </is>
       </c>
-      <c r="L98" s="4" t="n">
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M98" s="4" t="n">
         <v>3060</v>
       </c>
-      <c r="M98" s="4" t="inlineStr">
+      <c r="N98" s="4" t="inlineStr">
         <is>
           <t>3.1.3.1.2.1.27</t>
         </is>
       </c>
-      <c r="N98" s="4" t="inlineStr">
+      <c r="O98" s="4" t="inlineStr">
         <is>
           <t>Publicidade e Propaganda</t>
         </is>
       </c>
-      <c r="O98" s="8" t="inlineStr">
+      <c r="P98" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P98" s="4" t="inlineStr">
-        <is>
-          <t>Publicidade e propaganda. Administrativa: 2685.</t>
+      <c r="Q98" s="4" t="inlineStr">
+        <is>
+          <t>Publicidade e propaganda. Administrativa: 2685. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -7711,27 +8202,32 @@
           <t>CC318</t>
         </is>
       </c>
-      <c r="L99" s="4" t="n">
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M99" s="4" t="n">
         <v>2872</v>
       </c>
-      <c r="M99" s="4" t="inlineStr">
+      <c r="N99" s="4" t="inlineStr">
         <is>
           <t>1.1.1.2.5</t>
         </is>
       </c>
-      <c r="N99" s="4" t="inlineStr">
+      <c r="O99" s="4" t="inlineStr">
         <is>
           <t>Transferência de recursos</t>
         </is>
       </c>
-      <c r="O99" s="8" t="inlineStr">
+      <c r="P99" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P99" s="4" t="inlineStr">
-        <is>
-          <t>Transferência entre Matriz e Filial. Confirmar se o escritório usa 2872 (Transferência de recursos) ou mútuo (3086/2861).</t>
+      <c r="Q99" s="4" t="inlineStr">
+        <is>
+          <t>Transferência entre Matriz e Filial. Confirmar se o escritório usa 2872 (Transferência de recursos) ou mútuo (3086/2861). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -7783,27 +8279,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L100" s="4" t="n">
+      <c r="L100" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M100" s="4" t="n">
         <v>2511</v>
       </c>
-      <c r="M100" s="4" t="inlineStr">
+      <c r="N100" s="4" t="inlineStr">
         <is>
           <t>2.1.1.4.2.1</t>
         </is>
       </c>
-      <c r="N100" s="4" t="inlineStr">
+      <c r="O100" s="4" t="inlineStr">
         <is>
           <t>ICMS a Recolher</t>
         </is>
       </c>
-      <c r="O100" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P100" s="4" t="inlineStr">
-        <is>
-          <t>Recolhimento de ICMS (competência 08/26).</t>
+      <c r="P100" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q100" s="4" t="inlineStr">
+        <is>
+          <t>Recolhimento de ICMS (competência 08/26). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -7855,25 +8356,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L101" s="4" t="n">
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M101" s="4" t="n">
         <v>2628</v>
       </c>
-      <c r="M101" s="4" t="inlineStr">
+      <c r="N101" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.2.1.1</t>
         </is>
       </c>
-      <c r="N101" s="4" t="inlineStr">
+      <c r="O101" s="4" t="inlineStr">
         <is>
           <t>Honorarios Contabeis</t>
         </is>
       </c>
-      <c r="O101" s="7" t="inlineStr">
+      <c r="P101" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P101" s="4" t="inlineStr">
+      <c r="Q101" s="4" t="inlineStr">
         <is>
           <t>Honorários contábeis.</t>
         </is>
@@ -7927,27 +8433,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L102" s="4" t="n">
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M102" s="4" t="n">
         <v>3112</v>
       </c>
-      <c r="M102" s="4" t="inlineStr">
+      <c r="N102" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.1.17.8.16</t>
         </is>
       </c>
-      <c r="N102" s="4" t="inlineStr">
+      <c r="O102" s="4" t="inlineStr">
         <is>
           <t>Benefícios</t>
         </is>
       </c>
-      <c r="O102" s="8" t="inlineStr">
+      <c r="P102" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P102" s="4" t="inlineStr">
-        <is>
-          <t>Taxa/benefício VR. Alternativa: 3046.</t>
+      <c r="Q102" s="4" t="inlineStr">
+        <is>
+          <t>Taxa/benefício VR. Alternativa: 3046. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -7999,27 +8510,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L103" s="4" t="n">
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M103" s="4" t="n">
         <v>2859</v>
       </c>
-      <c r="M103" s="4" t="inlineStr">
+      <c r="N103" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.4</t>
         </is>
       </c>
-      <c r="N103" s="4" t="inlineStr">
+      <c r="O103" s="4" t="inlineStr">
         <is>
           <t>Licenciamento, Manutenção e Assinaturas Softwares Terceiros</t>
         </is>
       </c>
-      <c r="O103" s="8" t="inlineStr">
+      <c r="P103" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P103" s="4" t="inlineStr">
-        <is>
-          <t>Licenciamento/manutenção de software de terceiros. Alternativa (custo de serviço): 2839.</t>
+      <c r="Q103" s="4" t="inlineStr">
+        <is>
+          <t>Licenciamento/manutenção de software de terceiros. Alternativa (custo de serviço): 2839. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -8067,27 +8583,32 @@
           <t>CC341</t>
         </is>
       </c>
-      <c r="L104" s="4" t="n">
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M104" s="4" t="n">
         <v>3067</v>
       </c>
-      <c r="M104" s="4" t="inlineStr">
+      <c r="N104" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.3</t>
         </is>
       </c>
-      <c r="N104" s="4" t="inlineStr">
+      <c r="O104" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiros (PJ)</t>
         </is>
       </c>
-      <c r="O104" s="9" t="inlineStr">
+      <c r="P104" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P104" s="4" t="inlineStr">
-        <is>
-          <t>Mesmo fornecedor/categoria RSV Transf. Digital: confirmar natureza.</t>
+      <c r="Q104" s="4" t="inlineStr">
+        <is>
+          <t>Mesmo fornecedor/categoria RSV Transf. Digital: confirmar natureza. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -8139,27 +8660,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L105" s="4" t="n">
+      <c r="L105" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M105" s="4" t="n">
         <v>2822</v>
       </c>
-      <c r="M105" s="4" t="inlineStr">
+      <c r="N105" s="4" t="inlineStr">
         <is>
           <t>2.1.1.4.12</t>
         </is>
       </c>
-      <c r="N105" s="4" t="inlineStr">
+      <c r="O105" s="4" t="inlineStr">
         <is>
           <t>PIS/COFINS/CSLL a recolher</t>
         </is>
       </c>
-      <c r="O105" s="8" t="inlineStr">
+      <c r="P105" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P105" s="4" t="inlineStr">
-        <is>
-          <t>DARF ligado à NF do fornecedor (nº/U): retenção PIS/COFINS/CSLL. Confirmar o tributo.</t>
+      <c r="Q105" s="4" t="inlineStr">
+        <is>
+          <t>DARF ligado à NF do fornecedor (nº/U): retenção PIS/COFINS/CSLL. Confirmar o tributo. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -8211,27 +8737,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L106" s="4" t="n">
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M106" s="4" t="n">
         <v>2822</v>
       </c>
-      <c r="M106" s="4" t="inlineStr">
+      <c r="N106" s="4" t="inlineStr">
         <is>
           <t>2.1.1.4.12</t>
         </is>
       </c>
-      <c r="N106" s="4" t="inlineStr">
+      <c r="O106" s="4" t="inlineStr">
         <is>
           <t>PIS/COFINS/CSLL a recolher</t>
         </is>
       </c>
-      <c r="O106" s="8" t="inlineStr">
+      <c r="P106" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P106" s="4" t="inlineStr">
-        <is>
-          <t>DARF ligado à NF do fornecedor (nº/U): retenção PIS/COFINS/CSLL. Confirmar o tributo.</t>
+      <c r="Q106" s="4" t="inlineStr">
+        <is>
+          <t>DARF ligado à NF do fornecedor (nº/U): retenção PIS/COFINS/CSLL. Confirmar o tributo. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -8283,27 +8814,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L107" s="4" t="n">
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M107" s="4" t="n">
         <v>2822</v>
       </c>
-      <c r="M107" s="4" t="inlineStr">
+      <c r="N107" s="4" t="inlineStr">
         <is>
           <t>2.1.1.4.12</t>
         </is>
       </c>
-      <c r="N107" s="4" t="inlineStr">
+      <c r="O107" s="4" t="inlineStr">
         <is>
           <t>PIS/COFINS/CSLL a recolher</t>
         </is>
       </c>
-      <c r="O107" s="8" t="inlineStr">
+      <c r="P107" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P107" s="4" t="inlineStr">
-        <is>
-          <t>DARF ligado à NF do fornecedor (nº/U): retenção PIS/COFINS/CSLL. Confirmar o tributo.</t>
+      <c r="Q107" s="4" t="inlineStr">
+        <is>
+          <t>DARF ligado à NF do fornecedor (nº/U): retenção PIS/COFINS/CSLL. Confirmar o tributo. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -8355,27 +8891,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L108" s="4" t="n">
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M108" s="4" t="n">
         <v>2822</v>
       </c>
-      <c r="M108" s="4" t="inlineStr">
+      <c r="N108" s="4" t="inlineStr">
         <is>
           <t>2.1.1.4.12</t>
         </is>
       </c>
-      <c r="N108" s="4" t="inlineStr">
+      <c r="O108" s="4" t="inlineStr">
         <is>
           <t>PIS/COFINS/CSLL a recolher</t>
         </is>
       </c>
-      <c r="O108" s="8" t="inlineStr">
+      <c r="P108" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P108" s="4" t="inlineStr">
-        <is>
-          <t>DARF ligado à NF do fornecedor (nº/U): retenção PIS/COFINS/CSLL. Confirmar o tributo.</t>
+      <c r="Q108" s="4" t="inlineStr">
+        <is>
+          <t>DARF ligado à NF do fornecedor (nº/U): retenção PIS/COFINS/CSLL. Confirmar o tributo. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -8427,25 +8968,30 @@
           <t>CC644</t>
         </is>
       </c>
-      <c r="L109" s="4" t="n">
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>Consultoria / CS</t>
+        </is>
+      </c>
+      <c r="M109" s="4" t="n">
         <v>3065</v>
       </c>
-      <c r="M109" s="4" t="inlineStr">
+      <c r="N109" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.1</t>
         </is>
       </c>
-      <c r="N109" s="4" t="inlineStr">
+      <c r="O109" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Consultores)</t>
         </is>
       </c>
-      <c r="O109" s="7" t="inlineStr">
+      <c r="P109" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P109" s="4" t="inlineStr">
+      <c r="Q109" s="4" t="inlineStr">
         <is>
           <t>Custo de serviço terceiro - Consultores.</t>
         </is>
@@ -8499,25 +9045,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L110" s="4" t="n">
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M110" s="4" t="n">
         <v>3044</v>
       </c>
-      <c r="M110" s="4" t="inlineStr">
+      <c r="N110" s="4" t="inlineStr">
         <is>
           <t>2.1.1.1.5.4</t>
         </is>
       </c>
-      <c r="N110" s="4" t="inlineStr">
+      <c r="O110" s="4" t="inlineStr">
         <is>
           <t>Plano de Saúde Colaboradores</t>
         </is>
       </c>
-      <c r="O110" s="7" t="inlineStr">
+      <c r="P110" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P110" s="4" t="inlineStr">
+      <c r="Q110" s="4" t="inlineStr">
         <is>
           <t>Plano de saúde dos colaboradores.</t>
         </is>
@@ -8571,25 +9122,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L111" s="4" t="n">
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M111" s="4" t="n">
         <v>3044</v>
       </c>
-      <c r="M111" s="4" t="inlineStr">
+      <c r="N111" s="4" t="inlineStr">
         <is>
           <t>2.1.1.1.5.4</t>
         </is>
       </c>
-      <c r="N111" s="4" t="inlineStr">
+      <c r="O111" s="4" t="inlineStr">
         <is>
           <t>Plano de Saúde Colaboradores</t>
         </is>
       </c>
-      <c r="O111" s="7" t="inlineStr">
+      <c r="P111" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P111" s="4" t="inlineStr">
+      <c r="Q111" s="4" t="inlineStr">
         <is>
           <t>Plano de saúde dos colaboradores.</t>
         </is>
@@ -8643,27 +9199,32 @@
           <t>CC744</t>
         </is>
       </c>
-      <c r="L112" s="4" t="n">
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M112" s="4" t="n">
         <v>3133</v>
       </c>
-      <c r="M112" s="4" t="inlineStr">
+      <c r="N112" s="4" t="inlineStr">
         <is>
           <t>3.1.3.1.2.1.28</t>
         </is>
       </c>
-      <c r="N112" s="4" t="inlineStr">
+      <c r="O112" s="4" t="inlineStr">
         <is>
           <t>Brindes/Presentes para Clientes</t>
         </is>
       </c>
-      <c r="O112" s="8" t="inlineStr">
+      <c r="P112" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P112" s="4" t="inlineStr">
-        <is>
-          <t>Brindes/presentes para clientes. Se for propaganda: 3060.</t>
+      <c r="Q112" s="4" t="inlineStr">
+        <is>
+          <t>Brindes/presentes para clientes. Se for propaganda: 3060. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -8715,25 +9276,30 @@
           <t>CC506</t>
         </is>
       </c>
-      <c r="L113" s="4" t="n">
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>Qualidade</t>
+        </is>
+      </c>
+      <c r="M113" s="4" t="n">
         <v>3138</v>
       </c>
-      <c r="M113" s="4" t="inlineStr">
+      <c r="N113" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.5</t>
         </is>
       </c>
-      <c r="N113" s="4" t="inlineStr">
+      <c r="O113" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Qualidade)</t>
         </is>
       </c>
-      <c r="O113" s="7" t="inlineStr">
+      <c r="P113" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P113" s="4" t="inlineStr">
+      <c r="Q113" s="4" t="inlineStr">
         <is>
           <t>Custo de serviço terceiro - Qualidade.</t>
         </is>
@@ -8779,25 +9345,30 @@
         </is>
       </c>
       <c r="K114" s="4" t="inlineStr"/>
-      <c r="L114" s="4" t="n">
+      <c r="L114" s="4" t="inlineStr">
+        <is>
+          <t>sem CC</t>
+        </is>
+      </c>
+      <c r="M114" s="4" t="n">
         <v>2656</v>
       </c>
-      <c r="M114" s="4" t="inlineStr">
+      <c r="N114" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.17</t>
         </is>
       </c>
-      <c r="N114" s="4" t="inlineStr">
+      <c r="O114" s="4" t="inlineStr">
         <is>
           <t>Confraternizações, Eventos e Presentes</t>
         </is>
       </c>
-      <c r="O114" s="9" t="inlineStr">
+      <c r="P114" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P114" s="4" t="inlineStr">
+      <c r="Q114" s="4" t="inlineStr">
         <is>
           <t>Compra de doces: confraternização/presentes? Confirmar.</t>
         </is>
@@ -8851,25 +9422,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L115" s="4" t="n">
+      <c r="L115" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M115" s="4" t="n">
         <v>2838</v>
       </c>
-      <c r="M115" s="4" t="inlineStr">
+      <c r="N115" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.54</t>
         </is>
       </c>
-      <c r="N115" s="4" t="inlineStr">
+      <c r="O115" s="4" t="inlineStr">
         <is>
           <t>Copa e Cozinha</t>
         </is>
       </c>
-      <c r="O115" s="7" t="inlineStr">
+      <c r="P115" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P115" s="4" t="inlineStr">
+      <c r="Q115" s="4" t="inlineStr">
         <is>
           <t>Copa e cozinha.</t>
         </is>
@@ -8923,25 +9499,30 @@
           <t>CC506</t>
         </is>
       </c>
-      <c r="L116" s="4" t="n">
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>Qualidade</t>
+        </is>
+      </c>
+      <c r="M116" s="4" t="n">
         <v>3138</v>
       </c>
-      <c r="M116" s="4" t="inlineStr">
+      <c r="N116" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.5</t>
         </is>
       </c>
-      <c r="N116" s="4" t="inlineStr">
+      <c r="O116" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Qualidade)</t>
         </is>
       </c>
-      <c r="O116" s="7" t="inlineStr">
+      <c r="P116" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P116" s="4" t="inlineStr">
+      <c r="Q116" s="4" t="inlineStr">
         <is>
           <t>Custo de serviço terceiro - Qualidade.</t>
         </is>
@@ -8987,25 +9568,30 @@
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr"/>
-      <c r="L117" s="4" t="n">
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>sem CC</t>
+        </is>
+      </c>
+      <c r="M117" s="4" t="n">
         <v>2649</v>
       </c>
-      <c r="M117" s="4" t="inlineStr">
+      <c r="N117" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.10</t>
         </is>
       </c>
-      <c r="N117" s="4" t="inlineStr">
+      <c r="O117" s="4" t="inlineStr">
         <is>
           <t>Bens de Pequeno Valor</t>
         </is>
       </c>
-      <c r="O117" s="9" t="inlineStr">
+      <c r="P117" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P117" s="4" t="inlineStr">
+      <c r="Q117" s="4" t="inlineStr">
         <is>
           <t>Compra AC (sem categoria gerencial no extrato): bem de pequeno valor/material. Confirmar.</t>
         </is>
@@ -9051,25 +9637,30 @@
         </is>
       </c>
       <c r="K118" s="4" t="inlineStr"/>
-      <c r="L118" s="4" t="n">
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>sem CC</t>
+        </is>
+      </c>
+      <c r="M118" s="4" t="n">
         <v>2661</v>
       </c>
-      <c r="M118" s="4" t="inlineStr">
+      <c r="N118" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.22</t>
         </is>
       </c>
-      <c r="N118" s="4" t="inlineStr">
+      <c r="O118" s="4" t="inlineStr">
         <is>
           <t>Informatica (Consertos e Pecas) Adm</t>
         </is>
       </c>
-      <c r="O118" s="9" t="inlineStr">
+      <c r="P118" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P118" s="4" t="inlineStr">
+      <c r="Q118" s="4" t="inlineStr">
         <is>
           <t>Informática (infra/peças). Confirmar.</t>
         </is>
@@ -9123,27 +9714,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L119" s="4" t="n">
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M119" s="4" t="n">
         <v>2530</v>
       </c>
-      <c r="M119" s="4" t="inlineStr">
+      <c r="N119" s="4" t="inlineStr">
         <is>
           <t>2.1.1.1.2.2</t>
         </is>
       </c>
-      <c r="N119" s="4" t="inlineStr">
+      <c r="O119" s="4" t="inlineStr">
         <is>
           <t>FGTS a Recolher</t>
         </is>
       </c>
-      <c r="O119" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P119" s="4" t="inlineStr">
-        <is>
-          <t>Recolhimento de FGTS.</t>
+      <c r="P119" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q119" s="4" t="inlineStr">
+        <is>
+          <t>Recolhimento de FGTS. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -9195,25 +9791,30 @@
           <t>CC644</t>
         </is>
       </c>
-      <c r="L120" s="4" t="n">
+      <c r="L120" s="4" t="inlineStr">
+        <is>
+          <t>Consultoria / CS</t>
+        </is>
+      </c>
+      <c r="M120" s="4" t="n">
         <v>3065</v>
       </c>
-      <c r="M120" s="4" t="inlineStr">
+      <c r="N120" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.1</t>
         </is>
       </c>
-      <c r="N120" s="4" t="inlineStr">
+      <c r="O120" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Consultores)</t>
         </is>
       </c>
-      <c r="O120" s="7" t="inlineStr">
+      <c r="P120" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P120" s="4" t="inlineStr">
+      <c r="Q120" s="4" t="inlineStr">
         <is>
           <t>Custo de serviço terceiro - Consultores.</t>
         </is>
@@ -9267,27 +9868,32 @@
           <t>CC744</t>
         </is>
       </c>
-      <c r="L121" s="4" t="n">
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M121" s="4" t="n">
         <v>3060</v>
       </c>
-      <c r="M121" s="4" t="inlineStr">
+      <c r="N121" s="4" t="inlineStr">
         <is>
           <t>3.1.3.1.2.1.27</t>
         </is>
       </c>
-      <c r="N121" s="4" t="inlineStr">
+      <c r="O121" s="4" t="inlineStr">
         <is>
           <t>Publicidade e Propaganda</t>
         </is>
       </c>
-      <c r="O121" s="8" t="inlineStr">
+      <c r="P121" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P121" s="4" t="inlineStr">
-        <is>
-          <t>Publicidade e propaganda. Administrativa: 2685.</t>
+      <c r="Q121" s="4" t="inlineStr">
+        <is>
+          <t>Publicidade e propaganda. Administrativa: 2685. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -9339,27 +9945,32 @@
           <t>CC344</t>
         </is>
       </c>
-      <c r="L122" s="4" t="n">
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M122" s="4" t="n">
         <v>3139</v>
       </c>
-      <c r="M122" s="4" t="inlineStr">
+      <c r="N122" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.6</t>
         </is>
       </c>
-      <c r="N122" s="4" t="inlineStr">
+      <c r="O122" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Desenvolvedor)</t>
         </is>
       </c>
-      <c r="O122" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P122" s="4" t="inlineStr">
-        <is>
-          <t>Custo de serviço terceiro - Desenvolvedor.</t>
+      <c r="P122" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q122" s="4" t="inlineStr">
+        <is>
+          <t>Custo de serviço terceiro - Desenvolvedor. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -9411,25 +10022,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L123" s="4" t="n">
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M123" s="4" t="n">
         <v>2657</v>
       </c>
-      <c r="M123" s="4" t="inlineStr">
+      <c r="N123" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.18</t>
         </is>
       </c>
-      <c r="N123" s="4" t="inlineStr">
+      <c r="O123" s="4" t="inlineStr">
         <is>
           <t>Comunicacao / Telefone (adm.)</t>
         </is>
       </c>
-      <c r="O123" s="7" t="inlineStr">
+      <c r="P123" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P123" s="4" t="inlineStr">
+      <c r="Q123" s="4" t="inlineStr">
         <is>
           <t>Telefone/comunicação.</t>
         </is>
@@ -9483,25 +10099,30 @@
           <t>CC345</t>
         </is>
       </c>
-      <c r="L124" s="4" t="n">
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>Suporte</t>
+        </is>
+      </c>
+      <c r="M124" s="4" t="n">
         <v>3050</v>
       </c>
-      <c r="M124" s="4" t="inlineStr">
+      <c r="N124" s="4" t="inlineStr">
         <is>
           <t>2.1.1.1.5.10</t>
         </is>
       </c>
-      <c r="N124" s="4" t="inlineStr">
+      <c r="O124" s="4" t="inlineStr">
         <is>
           <t>Vale Transporte Funcionários</t>
         </is>
       </c>
-      <c r="O124" s="7" t="inlineStr">
+      <c r="P124" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P124" s="4" t="inlineStr">
+      <c r="Q124" s="4" t="inlineStr">
         <is>
           <t>Vale-transporte de funcionários.</t>
         </is>
@@ -9555,27 +10176,32 @@
           <t>CC346</t>
         </is>
       </c>
-      <c r="L125" s="4" t="n">
+      <c r="L125" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M125" s="4" t="n">
         <v>3113</v>
       </c>
-      <c r="M125" s="4" t="inlineStr">
+      <c r="N125" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.1.17.8.17</t>
         </is>
       </c>
-      <c r="N125" s="4" t="inlineStr">
+      <c r="O125" s="4" t="inlineStr">
         <is>
           <t>Recrutamento e Seleção</t>
         </is>
       </c>
-      <c r="O125" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P125" s="4" t="inlineStr">
-        <is>
-          <t>Recrutamento e seleção.</t>
+      <c r="P125" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q125" s="4" t="inlineStr">
+        <is>
+          <t>Recrutamento e seleção. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -9627,27 +10253,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L126" s="4" t="n">
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M126" s="4" t="n">
         <v>2529</v>
       </c>
-      <c r="M126" s="4" t="inlineStr">
+      <c r="N126" s="4" t="inlineStr">
         <is>
           <t>2.1.1.1.2.1</t>
         </is>
       </c>
-      <c r="N126" s="4" t="inlineStr">
+      <c r="O126" s="4" t="inlineStr">
         <is>
           <t>Contrib. Sindical a Recolher</t>
         </is>
       </c>
-      <c r="O126" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P126" s="4" t="inlineStr">
-        <is>
-          <t>Contribuição sindical a recolher.</t>
+      <c r="P126" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q126" s="4" t="inlineStr">
+        <is>
+          <t>Contribuição sindical a recolher. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -9699,27 +10330,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L127" s="4" t="n">
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M127" s="4" t="n">
         <v>2516</v>
       </c>
-      <c r="M127" s="4" t="inlineStr">
+      <c r="N127" s="4" t="inlineStr">
         <is>
           <t>2.1.1.4.2.6</t>
         </is>
       </c>
-      <c r="N127" s="4" t="inlineStr">
+      <c r="O127" s="4" t="inlineStr">
         <is>
           <t>ISS a Recolher</t>
         </is>
       </c>
-      <c r="O127" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P127" s="4" t="inlineStr">
-        <is>
-          <t>Recolhimento de ISS (competência 08/26).</t>
+      <c r="P127" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q127" s="4" t="inlineStr">
+        <is>
+          <t>Recolhimento de ISS (competência 08/26). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -9771,27 +10407,32 @@
           <t>CC830</t>
         </is>
       </c>
-      <c r="L128" s="4" t="n">
+      <c r="L128" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M128" s="4" t="n">
         <v>2587</v>
       </c>
-      <c r="M128" s="4" t="inlineStr">
+      <c r="N128" s="4" t="inlineStr">
         <is>
           <t>3.1.3.1.2.1.4</t>
         </is>
       </c>
-      <c r="N128" s="4" t="inlineStr">
+      <c r="O128" s="4" t="inlineStr">
         <is>
           <t>Despesas com Viagens/Hospedagem</t>
         </is>
       </c>
-      <c r="O128" s="8" t="inlineStr">
+      <c r="P128" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P128" s="4" t="inlineStr">
-        <is>
-          <t>Hospedagem (despesa comercial). Se for administrativa: 2647 Viagens.</t>
+      <c r="Q128" s="4" t="inlineStr">
+        <is>
+          <t>Hospedagem (despesa comercial). Se for administrativa: 2647 Viagens. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -9843,27 +10484,32 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L129" s="4" t="n">
+      <c r="L129" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M129" s="4" t="n">
         <v>3059</v>
       </c>
-      <c r="M129" s="4" t="inlineStr">
+      <c r="N129" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.61</t>
         </is>
       </c>
-      <c r="N129" s="4" t="inlineStr">
+      <c r="O129" s="4" t="inlineStr">
         <is>
           <t>Internet</t>
         </is>
       </c>
-      <c r="O129" s="8" t="inlineStr">
+      <c r="P129" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P129" s="4" t="inlineStr">
-        <is>
-          <t>Internet/link dedicado. Telefonia: 2657.</t>
+      <c r="Q129" s="4" t="inlineStr">
+        <is>
+          <t>Internet/link dedicado.</t>
         </is>
       </c>
     </row>
@@ -9915,25 +10561,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L130" s="4" t="n">
+      <c r="L130" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M130" s="4" t="n">
         <v>2657</v>
       </c>
-      <c r="M130" s="4" t="inlineStr">
+      <c r="N130" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.18</t>
         </is>
       </c>
-      <c r="N130" s="4" t="inlineStr">
+      <c r="O130" s="4" t="inlineStr">
         <is>
           <t>Comunicacao / Telefone (adm.)</t>
         </is>
       </c>
-      <c r="O130" s="7" t="inlineStr">
+      <c r="P130" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P130" s="4" t="inlineStr">
+      <c r="Q130" s="4" t="inlineStr">
         <is>
           <t>Telefone/comunicação.</t>
         </is>
@@ -9987,27 +10638,32 @@
           <t>CC744</t>
         </is>
       </c>
-      <c r="L131" s="4" t="n">
+      <c r="L131" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M131" s="4" t="n">
         <v>3133</v>
       </c>
-      <c r="M131" s="4" t="inlineStr">
+      <c r="N131" s="4" t="inlineStr">
         <is>
           <t>3.1.3.1.2.1.28</t>
         </is>
       </c>
-      <c r="N131" s="4" t="inlineStr">
+      <c r="O131" s="4" t="inlineStr">
         <is>
           <t>Brindes/Presentes para Clientes</t>
         </is>
       </c>
-      <c r="O131" s="8" t="inlineStr">
+      <c r="P131" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P131" s="4" t="inlineStr">
-        <is>
-          <t>Brindes/presentes para clientes. Se for propaganda: 3060.</t>
+      <c r="Q131" s="4" t="inlineStr">
+        <is>
+          <t>Brindes/presentes para clientes. Se for propaganda: 3060. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -10059,27 +10715,32 @@
           <t>CC318</t>
         </is>
       </c>
-      <c r="L132" s="4" t="n">
-        <v>3085</v>
-      </c>
-      <c r="M132" s="4" t="inlineStr">
-        <is>
-          <t>2.1.1.3.4</t>
-        </is>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M132" s="4" t="n">
+        <v>3086</v>
       </c>
       <c r="N132" s="4" t="inlineStr">
         <is>
-          <t>Empréstimo de Mútuo DCK</t>
-        </is>
-      </c>
-      <c r="O132" s="8" t="inlineStr">
+          <t>1.1.2.6.3</t>
+        </is>
+      </c>
+      <c r="O132" s="4" t="inlineStr">
+        <is>
+          <t>Empréstimo DCK Serviços Ltda/KORP(Intercompany)</t>
+        </is>
+      </c>
+      <c r="P132" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P132" s="4" t="inlineStr">
-        <is>
-          <t>Empréstimo/mútuo recebido da DCK. Alternativa: 2861 (DCK/KORP Intercompany).</t>
+      <c r="Q132" s="4" t="inlineStr">
+        <is>
+          <t>Empréstimo entre Matriz e Filial (mútuo intercompany). Confirmar conta com a contrapartida na outra empresa. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -10131,27 +10792,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L133" s="4" t="n">
+      <c r="L133" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M133" s="4" t="n">
         <v>2531</v>
       </c>
-      <c r="M133" s="4" t="inlineStr">
+      <c r="N133" s="4" t="inlineStr">
         <is>
           <t>2.1.1.1.2.3</t>
         </is>
       </c>
-      <c r="N133" s="4" t="inlineStr">
+      <c r="O133" s="4" t="inlineStr">
         <is>
           <t>INSS a Recolher</t>
         </is>
       </c>
-      <c r="O133" s="9" t="inlineStr">
+      <c r="P133" s="9" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="P133" s="4" t="inlineStr">
-        <is>
-          <t>DARF unificado: separar INSS (2531) e IRRF (2533) conforme a guia; o extrato traz o valor total.</t>
+      <c r="Q133" s="4" t="inlineStr">
+        <is>
+          <t>DARF unificado: separar INSS (2531) e IRRF (2533) conforme a guia; o extrato traz o valor total. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -10203,27 +10869,32 @@
           <t>CC616</t>
         </is>
       </c>
-      <c r="L134" s="4" t="n">
+      <c r="L134" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M134" s="4" t="n">
         <v>2649</v>
       </c>
-      <c r="M134" s="4" t="inlineStr">
+      <c r="N134" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.10</t>
         </is>
       </c>
-      <c r="N134" s="4" t="inlineStr">
+      <c r="O134" s="4" t="inlineStr">
         <is>
           <t>Bens de Pequeno Valor</t>
         </is>
       </c>
-      <c r="O134" s="8" t="inlineStr">
+      <c r="P134" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P134" s="4" t="inlineStr">
-        <is>
-          <t>Devolução de compra (estorno): creditar a mesma conta da despesa original.</t>
+      <c r="Q134" s="4" t="inlineStr">
+        <is>
+          <t>Devolução de compra (estorno): creditar a mesma conta da despesa original. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -10275,27 +10946,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L135" s="4" t="n">
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M135" s="4" t="n">
         <v>2698</v>
       </c>
-      <c r="M135" s="4" t="inlineStr">
+      <c r="N135" s="4" t="inlineStr">
         <is>
           <t>3.1.3.3.1.1</t>
         </is>
       </c>
-      <c r="N135" s="4" t="inlineStr">
+      <c r="O135" s="4" t="inlineStr">
         <is>
           <t>Despesas Bancarias</t>
         </is>
       </c>
-      <c r="O135" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P135" s="4" t="inlineStr">
-        <is>
-          <t>Tarifa bancária.</t>
+      <c r="P135" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q135" s="4" t="inlineStr">
+        <is>
+          <t>Tarifa bancária. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -10347,27 +11023,32 @@
           <t>CC616</t>
         </is>
       </c>
-      <c r="L136" s="4" t="n">
+      <c r="L136" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M136" s="4" t="n">
         <v>2649</v>
       </c>
-      <c r="M136" s="4" t="inlineStr">
+      <c r="N136" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.10</t>
         </is>
       </c>
-      <c r="N136" s="4" t="inlineStr">
+      <c r="O136" s="4" t="inlineStr">
         <is>
           <t>Bens de Pequeno Valor</t>
         </is>
       </c>
-      <c r="O136" s="8" t="inlineStr">
+      <c r="P136" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P136" s="4" t="inlineStr">
-        <is>
-          <t>Devolução de compra (estorno): creditar a mesma conta da despesa original.</t>
+      <c r="Q136" s="4" t="inlineStr">
+        <is>
+          <t>Devolução de compra (estorno): creditar a mesma conta da despesa original. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -10419,27 +11100,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L137" s="4" t="n">
+      <c r="L137" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M137" s="4" t="n">
         <v>2436</v>
       </c>
-      <c r="M137" s="4" t="inlineStr">
+      <c r="N137" s="4" t="inlineStr">
         <is>
           <t>1.1.2.1.1</t>
         </is>
       </c>
-      <c r="N137" s="4" t="inlineStr">
+      <c r="O137" s="4" t="inlineStr">
         <is>
           <t>Clientes a Receber</t>
         </is>
       </c>
-      <c r="O137" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P137" s="4" t="inlineStr">
-        <is>
-          <t>Baixa de duplicata/mensalidade de cliente.</t>
+      <c r="P137" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q137" s="4" t="inlineStr">
+        <is>
+          <t>Recebimento de cliente (baixa de duplicata/mensalidade). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -10491,27 +11177,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L138" s="4" t="n">
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M138" s="4" t="n">
         <v>2512</v>
       </c>
-      <c r="M138" s="4" t="inlineStr">
+      <c r="N138" s="4" t="inlineStr">
         <is>
           <t>2.1.1.4.2.2</t>
         </is>
       </c>
-      <c r="N138" s="4" t="inlineStr">
+      <c r="O138" s="4" t="inlineStr">
         <is>
           <t>PIS a Recolher</t>
         </is>
       </c>
-      <c r="O138" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P138" s="4" t="inlineStr">
-        <is>
-          <t>Recolhimento de PIS (competência 08/26).</t>
+      <c r="P138" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q138" s="4" t="inlineStr">
+        <is>
+          <t>Recolhimento de PIS (competência 08/26). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -10563,25 +11254,30 @@
           <t>CC320</t>
         </is>
       </c>
-      <c r="L139" s="4" t="n">
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>ADM geral</t>
+        </is>
+      </c>
+      <c r="M139" s="4" t="n">
         <v>2838</v>
       </c>
-      <c r="M139" s="4" t="inlineStr">
+      <c r="N139" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.54</t>
         </is>
       </c>
-      <c r="N139" s="4" t="inlineStr">
+      <c r="O139" s="4" t="inlineStr">
         <is>
           <t>Copa e Cozinha</t>
         </is>
       </c>
-      <c r="O139" s="7" t="inlineStr">
+      <c r="P139" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P139" s="4" t="inlineStr">
+      <c r="Q139" s="4" t="inlineStr">
         <is>
           <t>Copa e cozinha.</t>
         </is>
@@ -10635,27 +11331,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L140" s="4" t="n">
+      <c r="L140" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M140" s="4" t="n">
         <v>2859</v>
       </c>
-      <c r="M140" s="4" t="inlineStr">
+      <c r="N140" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.4</t>
         </is>
       </c>
-      <c r="N140" s="4" t="inlineStr">
+      <c r="O140" s="4" t="inlineStr">
         <is>
           <t>Licenciamento, Manutenção e Assinaturas Softwares Terceiros</t>
         </is>
       </c>
-      <c r="O140" s="8" t="inlineStr">
+      <c r="P140" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P140" s="4" t="inlineStr">
-        <is>
-          <t>Licenciamento/manutenção de software de terceiros. Alternativa (custo de serviço): 2839.</t>
+      <c r="Q140" s="4" t="inlineStr">
+        <is>
+          <t>Licenciamento/manutenção de software de terceiros. Alternativa (custo de serviço): 2839. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -10707,27 +11408,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L141" s="4" t="n">
+      <c r="L141" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M141" s="4" t="n">
         <v>2513</v>
       </c>
-      <c r="M141" s="4" t="inlineStr">
+      <c r="N141" s="4" t="inlineStr">
         <is>
           <t>2.1.1.4.2.3</t>
         </is>
       </c>
-      <c r="N141" s="4" t="inlineStr">
+      <c r="O141" s="4" t="inlineStr">
         <is>
           <t>COFINS a Recolher</t>
         </is>
       </c>
-      <c r="O141" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P141" s="4" t="inlineStr">
-        <is>
-          <t>Recolhimento de COFINS (competência 08/26).</t>
+      <c r="P141" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q141" s="4" t="inlineStr">
+        <is>
+          <t>Recolhimento de COFINS (competência 08/26). | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -10779,27 +11485,32 @@
           <t>CC318</t>
         </is>
       </c>
-      <c r="L142" s="4" t="n">
-        <v>2661</v>
-      </c>
-      <c r="M142" s="4" t="inlineStr">
-        <is>
-          <t>3.1.3.2.3.1.22</t>
-        </is>
+      <c r="L142" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M142" s="4" t="n">
+        <v>3086</v>
       </c>
       <c r="N142" s="4" t="inlineStr">
         <is>
-          <t>Informatica (Consertos e Pecas) Adm</t>
-        </is>
-      </c>
-      <c r="O142" s="9" t="inlineStr">
-        <is>
-          <t>Baixa</t>
-        </is>
-      </c>
-      <c r="P142" s="4" t="inlineStr">
-        <is>
-          <t>Informática (infra/peças). Confirmar.</t>
+          <t>1.1.2.6.3</t>
+        </is>
+      </c>
+      <c r="O142" s="4" t="inlineStr">
+        <is>
+          <t>Empréstimo DCK Serviços Ltda/KORP(Intercompany)</t>
+        </is>
+      </c>
+      <c r="P142" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q142" s="4" t="inlineStr">
+        <is>
+          <t>Empréstimo entre Matriz e Filial (mútuo intercompany). Confirmar conta com a contrapartida na outra empresa. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -10851,27 +11562,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L143" s="4" t="n">
+      <c r="L143" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M143" s="4" t="n">
         <v>3050</v>
       </c>
-      <c r="M143" s="4" t="inlineStr">
+      <c r="N143" s="4" t="inlineStr">
         <is>
           <t>2.1.1.1.5.10</t>
         </is>
       </c>
-      <c r="N143" s="4" t="inlineStr">
+      <c r="O143" s="4" t="inlineStr">
         <is>
           <t>Vale Transporte Funcionários</t>
         </is>
       </c>
-      <c r="O143" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P143" s="4" t="inlineStr">
-        <is>
-          <t>Vale-transporte de funcionários.</t>
+      <c r="P143" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q143" s="4" t="inlineStr">
+        <is>
+          <t>Vale-transporte de funcionários. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -10923,27 +11639,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L144" s="4" t="n">
+      <c r="L144" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M144" s="4" t="n">
         <v>3050</v>
       </c>
-      <c r="M144" s="4" t="inlineStr">
+      <c r="N144" s="4" t="inlineStr">
         <is>
           <t>2.1.1.1.5.10</t>
         </is>
       </c>
-      <c r="N144" s="4" t="inlineStr">
+      <c r="O144" s="4" t="inlineStr">
         <is>
           <t>Vale Transporte Funcionários</t>
         </is>
       </c>
-      <c r="O144" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P144" s="4" t="inlineStr">
-        <is>
-          <t>Vale-transporte de funcionários.</t>
+      <c r="P144" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q144" s="4" t="inlineStr">
+        <is>
+          <t>Vale-transporte de funcionários. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -10995,27 +11716,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L145" s="4" t="n">
+      <c r="L145" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M145" s="4" t="n">
         <v>3046</v>
       </c>
-      <c r="M145" s="4" t="inlineStr">
+      <c r="N145" s="4" t="inlineStr">
         <is>
           <t>2.1.1.1.5.6</t>
         </is>
       </c>
-      <c r="N145" s="4" t="inlineStr">
+      <c r="O145" s="4" t="inlineStr">
         <is>
           <t>Refeições</t>
         </is>
       </c>
-      <c r="O145" s="8" t="inlineStr">
+      <c r="P145" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P145" s="4" t="inlineStr">
-        <is>
-          <t>Vale-refeição/alimentação (Benefícios - Refeições). Alternativa: 3043 PAT.</t>
+      <c r="Q145" s="4" t="inlineStr">
+        <is>
+          <t>Vale-refeição/alimentação (Benefícios - Refeições). Alternativa: 3043 PAT. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -11067,27 +11793,32 @@
           <t>CC476</t>
         </is>
       </c>
-      <c r="L146" s="4" t="n">
+      <c r="L146" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M146" s="4" t="n">
         <v>3050</v>
       </c>
-      <c r="M146" s="4" t="inlineStr">
+      <c r="N146" s="4" t="inlineStr">
         <is>
           <t>2.1.1.1.5.10</t>
         </is>
       </c>
-      <c r="N146" s="4" t="inlineStr">
+      <c r="O146" s="4" t="inlineStr">
         <is>
           <t>Vale Transporte Funcionários</t>
         </is>
       </c>
-      <c r="O146" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="P146" s="4" t="inlineStr">
-        <is>
-          <t>Vale-transporte de funcionários.</t>
+      <c r="P146" s="7" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="Q146" s="4" t="inlineStr">
+        <is>
+          <t>Vale-transporte de funcionários. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -11139,25 +11870,30 @@
           <t>CC337</t>
         </is>
       </c>
-      <c r="L147" s="4" t="n">
+      <c r="L147" s="4" t="inlineStr">
+        <is>
+          <t>Desenvolvimento (DES)</t>
+        </is>
+      </c>
+      <c r="M147" s="4" t="n">
         <v>3139</v>
       </c>
-      <c r="M147" s="4" t="inlineStr">
+      <c r="N147" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.6</t>
         </is>
       </c>
-      <c r="N147" s="4" t="inlineStr">
+      <c r="O147" s="4" t="inlineStr">
         <is>
           <t>Custo Serviço Terceiro (Desenvolvedor)</t>
         </is>
       </c>
-      <c r="O147" s="7" t="inlineStr">
+      <c r="P147" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="P147" s="4" t="inlineStr">
+      <c r="Q147" s="4" t="inlineStr">
         <is>
           <t>Custo de serviço terceiro - Desenvolvedor.</t>
         </is>
@@ -11211,27 +11947,32 @@
           <t>CC384</t>
         </is>
       </c>
-      <c r="L148" s="4" t="n">
+      <c r="L148" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M148" s="4" t="n">
         <v>2859</v>
       </c>
-      <c r="M148" s="4" t="inlineStr">
+      <c r="N148" s="4" t="inlineStr">
         <is>
           <t>3.1.2.2.2.4</t>
         </is>
       </c>
-      <c r="N148" s="4" t="inlineStr">
+      <c r="O148" s="4" t="inlineStr">
         <is>
           <t>Licenciamento, Manutenção e Assinaturas Softwares Terceiros</t>
         </is>
       </c>
-      <c r="O148" s="8" t="inlineStr">
+      <c r="P148" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P148" s="4" t="inlineStr">
-        <is>
-          <t>Licenciamento/manutenção de software de terceiros. Alternativa (custo de serviço): 2839.</t>
+      <c r="Q148" s="4" t="inlineStr">
+        <is>
+          <t>Licenciamento/manutenção de software de terceiros. Alternativa (custo de serviço): 2839. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -11283,27 +12024,32 @@
           <t>CC833</t>
         </is>
       </c>
-      <c r="L149" s="4" t="n">
+      <c r="L149" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M149" s="4" t="n">
         <v>2664</v>
       </c>
-      <c r="M149" s="4" t="inlineStr">
+      <c r="N149" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.25</t>
         </is>
       </c>
-      <c r="N149" s="4" t="inlineStr">
+      <c r="O149" s="4" t="inlineStr">
         <is>
           <t>Material de Expediente</t>
         </is>
       </c>
-      <c r="O149" s="8" t="inlineStr">
+      <c r="P149" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P149" s="4" t="inlineStr">
-        <is>
-          <t>Cópias/material de expediente.</t>
+      <c r="Q149" s="4" t="inlineStr">
+        <is>
+          <t>Cópias/material de expediente. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
@@ -11355,32 +12101,37 @@
           <t>CC833</t>
         </is>
       </c>
-      <c r="L150" s="4" t="n">
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>CC sem de-para</t>
+        </is>
+      </c>
+      <c r="M150" s="4" t="n">
         <v>2664</v>
       </c>
-      <c r="M150" s="4" t="inlineStr">
+      <c r="N150" s="4" t="inlineStr">
         <is>
           <t>3.1.3.2.3.1.25</t>
         </is>
       </c>
-      <c r="N150" s="4" t="inlineStr">
+      <c r="O150" s="4" t="inlineStr">
         <is>
           <t>Material de Expediente</t>
         </is>
       </c>
-      <c r="O150" s="8" t="inlineStr">
+      <c r="P150" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="P150" s="4" t="inlineStr">
-        <is>
-          <t>Cópias/material de expediente.</t>
+      <c r="Q150" s="4" t="inlineStr">
+        <is>
+          <t>Cópias/material de expediente. | CC sem de-para de área: validar a conta pelo centro de custo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P150"/>
+  <autoFilter ref="A1:Q150"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11571,7 +12322,7 @@
           <t>Custo Serviço Terceiro (Consultores)</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
@@ -11623,7 +12374,7 @@
           <t>Transferência de recursos</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
